--- a/outputs/mecm_security_mapping/MECM读取信息到ServiceNow表字段映射_23项安全指摘_字段落表矩阵追加版.xlsx
+++ b/outputs/mecm_security_mapping/MECM读取信息到ServiceNow表字段映射_23项安全指摘_字段落表矩阵追加版.xlsx
@@ -2,17 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_结论" sheetId="1" r:id="R09c26702786e43da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_23项逐条映射" sheetId="2" r:id="Rf421f8f627d44132"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_推荐落表设计" sheetId="3" r:id="R3372126c562a4e35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_确认事项" sheetId="4" r:id="R6ab1e3388a304289"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_官方依据URL" sheetId="5" r:id="R2ae278a551a64027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_結論_JP" sheetId="6" r:id="R61396130609d4011"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_23項目Mapping_JP" sheetId="7" r:id="R24496f299f784fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_落表設計_JP" sheetId="8" r:id="R222dcf01acd649ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_確認事項_JP" sheetId="9" r:id="R6a122fa0a49d4947"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公式根拠URL_JP" sheetId="10" r:id="R50dc893e17ac4b7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_字段落表矩阵_CN" sheetId="11" r:id="Rc8109e97fa194151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_结论" sheetId="1" r:id="R1732f88ff5164c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_23项逐条映射" sheetId="2" r:id="R2d4e5aabcf2c4ebd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_推荐落表设计" sheetId="3" r:id="Rd32d3934526b4e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_确认事项" sheetId="4" r:id="Raa77847995634639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_官方依据URL" sheetId="5" r:id="R26ad02e33e5e4515"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_結論_JP" sheetId="6" r:id="R95fa58b5073d4a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_23項目Mapping_JP" sheetId="7" r:id="R1ce98e521393407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_落表設計_JP" sheetId="8" r:id="R595ec5652b2948e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_確認事項_JP" sheetId="9" r:id="R13c6f7b07b0549d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公式根拠URL_JP" sheetId="10" r:id="R7de18eed837c4e28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_字段落表矩阵_CN" sheetId="11" r:id="R8fa7f4dccf8646a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_フィールド格納マトリクス_JP" sheetId="12" r:id="Rf44a6872435f4f37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +65,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -109,6 +110,76 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF404040"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7FBFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7FBFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -263,7 +334,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="108">
+  <x:cellXfs count="172">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -542,6 +613,174 @@
     <x:xf numFmtId="0" fontId="6" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="22" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="26" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="30" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -8579,6 +8818,7297 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="6" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="29.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="31.25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="51.25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="21.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="55" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="33" customHeight="1">
+      <x:c r="A1" s="143" t="str">
+        <x:v>MECM セキュリティ指摘 23 項目：取得フィールドと ServiceNow 標準格納可否 O/X マトリクス</x:v>
+      </x:c>
+      <x:c r="B1" s="143"/>
+      <x:c r="C1" s="143"/>
+      <x:c r="D1" s="143"/>
+      <x:c r="E1" s="143"/>
+      <x:c r="F1" s="143"/>
+      <x:c r="G1" s="143"/>
+      <x:c r="H1" s="143"/>
+      <x:c r="I1" s="143"/>
+      <x:c r="J1" s="143"/>
+      <x:c r="K1" s="143"/>
+      <x:c r="L1" s="143"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="148" t="str">
+        <x:v>判定基準：O = ServiceNow 公式の SG-SCCM ターゲットクラス資料に標準ターゲットテーブル / 項目が明記されている。X = MECM では取得可能でも標準 Connector に対応項目がない、または顧客のライフサイクル・コンプライアンス・リスクルールによる算出結果である。O はすべての環境で値が必ず格納されることを意味しない。顧客環境の IntegrationHub ETL Data Map、プラグイン / SAM の有無、MECM の実インベントリ列を確認する。確認日：2026-06-24。</x:v>
+      </x:c>
+      <x:c r="B3" s="149"/>
+      <x:c r="C3" s="149"/>
+      <x:c r="D3" s="149"/>
+      <x:c r="E3" s="149"/>
+      <x:c r="F3" s="149"/>
+      <x:c r="G3" s="149"/>
+      <x:c r="H3" s="149"/>
+      <x:c r="I3" s="149"/>
+      <x:c r="J3" s="149"/>
+      <x:c r="K3" s="149"/>
+      <x:c r="L3" s="150"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="151"/>
+      <x:c r="B4" s="152"/>
+      <x:c r="C4" s="152"/>
+      <x:c r="D4" s="152"/>
+      <x:c r="E4" s="152"/>
+      <x:c r="F4" s="152"/>
+      <x:c r="G4" s="152"/>
+      <x:c r="H4" s="152"/>
+      <x:c r="I4" s="152"/>
+      <x:c r="J4" s="152"/>
+      <x:c r="K4" s="152"/>
+      <x:c r="L4" s="153"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="154"/>
+      <x:c r="B5" s="155"/>
+      <x:c r="C5" s="155"/>
+      <x:c r="D5" s="155"/>
+      <x:c r="E5" s="155"/>
+      <x:c r="F5" s="155"/>
+      <x:c r="G5" s="155"/>
+      <x:c r="H5" s="155"/>
+      <x:c r="I5" s="155"/>
+      <x:c r="J5" s="155"/>
+      <x:c r="K5" s="155"/>
+      <x:c r="L5" s="156"/>
+    </x:row>
+    <x:row r="7" ht="28.5" customHeight="1">
+      <x:c r="A7" s="158" t="str">
+        <x:v>フィールド行数</x:v>
+      </x:c>
+      <x:c r="B7" s="158" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C7" s="158" t="str">
+        <x:v>O：標準格納可能</x:v>
+      </x:c>
+      <x:c r="D7" s="158" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E7" s="158" t="str">
+        <x:v>X：標準では直接格納不可</x:v>
+      </x:c>
+      <x:c r="F7" s="158" t="n">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="28.5" customHeight="1">
+      <x:c r="A8" s="86" t="str">
+        <x:v>要点</x:v>
+      </x:c>
+      <x:c r="B8" s="86" t="str">
+        <x:v>端末 / OS / ソフトウェアインストール / ディスク識別情報などの基本資産項目は一部標準格納可能。一方、23 項目のセキュリティ指摘における最終判定の多くは、カスタムのセキュリティ発見またはコンプライアンステーブルで管理する必要がある。</x:v>
+      </x:c>
+      <x:c r="C8" s="86" t="str"/>
+      <x:c r="D8" s="86" t="str"/>
+      <x:c r="E8" s="86" t="str"/>
+      <x:c r="F8" s="86" t="str"/>
+    </x:row>
+    <x:row r="10" ht="40.5" customHeight="1">
+      <x:c r="A10" s="164" t="str">
+        <x:v>#</x:v>
+      </x:c>
+      <x:c r="B10" s="164" t="str">
+        <x:v>分類</x:v>
+      </x:c>
+      <x:c r="C10" s="164" t="str">
+        <x:v>指摘内容</x:v>
+      </x:c>
+      <x:c r="D10" s="164" t="str">
+        <x:v>具体的な取得情報</x:v>
+      </x:c>
+      <x:c r="E10" s="164" t="str">
+        <x:v>想定 MECM 項目 / 属性</x:v>
+      </x:c>
+      <x:c r="F10" s="164" t="str">
+        <x:v>MECM ソース</x:v>
+      </x:c>
+      <x:c r="G10" s="164" t="str">
+        <x:v>ServiceNow 標準テーブル</x:v>
+      </x:c>
+      <x:c r="H10" s="164" t="str">
+        <x:v>ServiceNow 標準フィールド</x:v>
+      </x:c>
+      <x:c r="I10" s="164" t="str">
+        <x:v>標準格納可否
+O / X</x:v>
+      </x:c>
+      <x:c r="J10" s="164" t="str">
+        <x:v>判定根拠</x:v>
+      </x:c>
+      <x:c r="K10" s="164" t="str">
+        <x:v>根拠レベル</x:v>
+      </x:c>
+      <x:c r="L10" s="164" t="str">
+        <x:v>参考資料 URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="63" customHeight="1">
+      <x:c r="A11" s="165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B11" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C11" s="166" t="str">
+        <x:v>OS サポート期限切れ</x:v>
+      </x:c>
+      <x:c r="D11" s="166" t="str">
+        <x:v>OS 名</x:v>
+      </x:c>
+      <x:c r="E11" s="166" t="str">
+        <x:v>Caption0 / Name0（候補）</x:v>
+      </x:c>
+      <x:c r="F11" s="166" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G11" s="166" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H11" s="166" t="str">
+        <x:v>os</x:v>
+      </x:c>
+      <x:c r="I11" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J11" s="166" t="str">
+        <x:v>ServiceNow 公式ターゲットクラス資料に cmdb_ci_computer.os が明記されている。</x:v>
+      </x:c>
+      <x:c r="K11" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L11" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="63" customHeight="1">
+      <x:c r="A12" s="165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B12" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C12" s="166" t="str">
+        <x:v>OS サポート期限切れ</x:v>
+      </x:c>
+      <x:c r="D12" s="166" t="str">
+        <x:v>OS バージョン</x:v>
+      </x:c>
+      <x:c r="E12" s="166" t="str">
+        <x:v>Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F12" s="166" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G12" s="166" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H12" s="166" t="str">
+        <x:v>os_version</x:v>
+      </x:c>
+      <x:c r="I12" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J12" s="166" t="str">
+        <x:v>ServiceNow 公式ターゲットクラス資料に cmdb_ci_computer.os_version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K12" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L12" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="63" customHeight="1">
+      <x:c r="A13" s="165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B13" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C13" s="166" t="str">
+        <x:v>OS サポート期限切れ</x:v>
+      </x:c>
+      <x:c r="D13" s="166" t="str">
+        <x:v>OS Service Pack</x:v>
+      </x:c>
+      <x:c r="E13" s="166" t="str">
+        <x:v>CSDVersion0 / ServicePackMajorVersion0（候補）</x:v>
+      </x:c>
+      <x:c r="F13" s="166" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G13" s="166" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H13" s="166" t="str">
+        <x:v>os_service_pack</x:v>
+      </x:c>
+      <x:c r="I13" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J13" s="166" t="str">
+        <x:v>標準ターゲット項目は存在する。実際の MECM 列名と変換内容は IntegrationHub ETL Data Map で確認する。</x:v>
+      </x:c>
+      <x:c r="K13" s="166" t="str">
+        <x:v>公式サポート・マッピング要確認</x:v>
+      </x:c>
+      <x:c r="L13" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="63" customHeight="1">
+      <x:c r="A14" s="165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C14" s="166" t="str">
+        <x:v>OS サポート期限切れ</x:v>
+      </x:c>
+      <x:c r="D14" s="166" t="str">
+        <x:v>OS Build Number</x:v>
+      </x:c>
+      <x:c r="E14" s="166" t="str">
+        <x:v>BuildNumber0（候補）</x:v>
+      </x:c>
+      <x:c r="F14" s="166" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G14" s="166" t="str">
+        <x:v>明確な標準ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H14" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I14" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J14" s="166" t="str">
+        <x:v>公式 SG-SCCM ターゲット項目一覧には独立した Build Number がない。カスタムマッピング、または os_version との組み合わせで表現する。</x:v>
+      </x:c>
+      <x:c r="K14" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L14" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="63" customHeight="1">
+      <x:c r="A15" s="165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B15" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C15" s="166" t="str">
+        <x:v>OS サポート期限切れ</x:v>
+      </x:c>
+      <x:c r="D15" s="166" t="str">
+        <x:v>最終ハードウェアインベントリ / 検出日時</x:v>
+      </x:c>
+      <x:c r="E15" s="166" t="str">
+        <x:v>LastHWScan（候補）</x:v>
+      </x:c>
+      <x:c r="F15" s="166" t="str">
+        <x:v>v_GS_WORKSTATION_STATUS</x:v>
+      </x:c>
+      <x:c r="G15" s="166" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H15" s="166" t="str">
+        <x:v>last_discovered</x:v>
+      </x:c>
+      <x:c r="I15" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J15" s="166" t="str">
+        <x:v>標準ターゲット項目に last_discovered が明記されている。ETL が LastHWScan を書き込むか確認が必要。</x:v>
+      </x:c>
+      <x:c r="K15" s="166" t="str">
+        <x:v>公式サポート・マッピング要確認</x:v>
+      </x:c>
+      <x:c r="L15" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="63" customHeight="1">
+      <x:c r="A16" s="165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B16" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C16" s="166" t="str">
+        <x:v>OS サポート期限切れ</x:v>
+      </x:c>
+      <x:c r="D16" s="166" t="str">
+        <x:v>サポート終了日</x:v>
+      </x:c>
+      <x:c r="E16" s="166" t="str">
+        <x:v>顧客ライフサイクルマスタの EOL Date</x:v>
+      </x:c>
+      <x:c r="F16" s="166" t="str">
+        <x:v>MECM の原始インベントリ項目ではない</x:v>
+      </x:c>
+      <x:c r="G16" s="166" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H16" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I16" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J16" s="166" t="str">
+        <x:v>顧客管理の OS ライフサイクルマスタとの照合が必要であり、標準 SG-SCCM はこの日付を生成しない。</x:v>
+      </x:c>
+      <x:c r="K16" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L16" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="63" customHeight="1">
+      <x:c r="A17" s="165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B17" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C17" s="166" t="str">
+        <x:v>OS サポート期限切れ</x:v>
+      </x:c>
+      <x:c r="D17" s="166" t="str">
+        <x:v>ライフサイクル段階 / EOL 判定結果</x:v>
+      </x:c>
+      <x:c r="E17" s="166" t="str">
+        <x:v>OS 名、バージョン、ライフサイクルマスタから算出</x:v>
+      </x:c>
+      <x:c r="F17" s="166" t="str">
+        <x:v>顧客ルールエンジン / 外部マスタ</x:v>
+      </x:c>
+      <x:c r="G17" s="166" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H17" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I17" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J17" s="166" t="str">
+        <x:v>MECM の基本資産項目ではなく、算出された監査結果である。カスタム finding テーブルへの格納を推奨する。</x:v>
+      </x:c>
+      <x:c r="K17" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L17" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="63" customHeight="1">
+      <x:c r="A18" s="99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B18" s="98" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C18" s="98" t="str">
+        <x:v>OS 移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D18" s="98" t="str">
+        <x:v>OS 名</x:v>
+      </x:c>
+      <x:c r="E18" s="98" t="str">
+        <x:v>Caption0 / Name0（候補）</x:v>
+      </x:c>
+      <x:c r="F18" s="98" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G18" s="98" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H18" s="98" t="str">
+        <x:v>os</x:v>
+      </x:c>
+      <x:c r="I18" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J18" s="98" t="str">
+        <x:v>ServiceNow 公式ターゲットクラス資料に cmdb_ci_computer.os が明記されている。</x:v>
+      </x:c>
+      <x:c r="K18" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L18" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="63" customHeight="1">
+      <x:c r="A19" s="99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B19" s="98" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C19" s="98" t="str">
+        <x:v>OS 移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D19" s="98" t="str">
+        <x:v>OS バージョン</x:v>
+      </x:c>
+      <x:c r="E19" s="98" t="str">
+        <x:v>Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F19" s="98" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G19" s="98" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H19" s="98" t="str">
+        <x:v>os_version</x:v>
+      </x:c>
+      <x:c r="I19" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J19" s="98" t="str">
+        <x:v>ServiceNow 公式ターゲットクラス資料に cmdb_ci_computer.os_version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K19" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L19" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="63" customHeight="1">
+      <x:c r="A20" s="99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B20" s="98" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C20" s="98" t="str">
+        <x:v>OS 移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D20" s="98" t="str">
+        <x:v>OS Service Pack</x:v>
+      </x:c>
+      <x:c r="E20" s="98" t="str">
+        <x:v>CSDVersion0 / ServicePackMajorVersion0（候補）</x:v>
+      </x:c>
+      <x:c r="F20" s="98" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G20" s="98" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H20" s="98" t="str">
+        <x:v>os_service_pack</x:v>
+      </x:c>
+      <x:c r="I20" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J20" s="98" t="str">
+        <x:v>標準ターゲット項目は存在する。実際の MECM 列名と変換内容は IntegrationHub ETL Data Map で確認する。</x:v>
+      </x:c>
+      <x:c r="K20" s="98" t="str">
+        <x:v>公式サポート・マッピング要確認</x:v>
+      </x:c>
+      <x:c r="L20" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="63" customHeight="1">
+      <x:c r="A21" s="99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B21" s="98" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C21" s="98" t="str">
+        <x:v>OS 移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D21" s="98" t="str">
+        <x:v>OS Build Number</x:v>
+      </x:c>
+      <x:c r="E21" s="98" t="str">
+        <x:v>BuildNumber0（候補）</x:v>
+      </x:c>
+      <x:c r="F21" s="98" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G21" s="98" t="str">
+        <x:v>明確な標準ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H21" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I21" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J21" s="98" t="str">
+        <x:v>標準ターゲット項目一覧に独立した Build Number はない。</x:v>
+      </x:c>
+      <x:c r="K21" s="98" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L21" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="63" customHeight="1">
+      <x:c r="A22" s="99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B22" s="98" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C22" s="98" t="str">
+        <x:v>OS 移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D22" s="98" t="str">
+        <x:v>移行期限日</x:v>
+      </x:c>
+      <x:c r="E22" s="98" t="str">
+        <x:v>顧客ライフサイクルマスタの Migration Due Date</x:v>
+      </x:c>
+      <x:c r="F22" s="98" t="str">
+        <x:v>MECM の原始インベントリ項目ではない</x:v>
+      </x:c>
+      <x:c r="G22" s="98" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H22" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I22" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J22" s="98" t="str">
+        <x:v>顧客マスタが必要であり、標準 SG-SCCM のマッピング項目ではない。</x:v>
+      </x:c>
+      <x:c r="K22" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L22" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="63" customHeight="1">
+      <x:c r="A23" s="99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B23" s="98" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C23" s="98" t="str">
+        <x:v>OS 移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D23" s="98" t="str">
+        <x:v>期限までの残日数</x:v>
+      </x:c>
+      <x:c r="E23" s="98" t="str">
+        <x:v>Migration Due Date - 判定日</x:v>
+      </x:c>
+      <x:c r="F23" s="98" t="str">
+        <x:v>算出項目</x:v>
+      </x:c>
+      <x:c r="G23" s="98" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H23" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I23" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J23" s="98" t="str">
+        <x:v>算出値のため、監査 / コンプライアンス結果テーブルへの格納を推奨する。</x:v>
+      </x:c>
+      <x:c r="K23" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L23" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="63" customHeight="1">
+      <x:c r="A24" s="99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B24" s="98" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C24" s="98" t="str">
+        <x:v>OS 移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D24" s="98" t="str">
+        <x:v>3 か月前警告判定</x:v>
+      </x:c>
+      <x:c r="E24" s="98" t="str">
+        <x:v>ライフサイクルルールの算出結果</x:v>
+      </x:c>
+      <x:c r="F24" s="98" t="str">
+        <x:v>顧客ルールエンジン</x:v>
+      </x:c>
+      <x:c r="G24" s="98" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H24" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I24" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J24" s="98" t="str">
+        <x:v>標準 CMDB は OS の基本属性を格納するが、顧客定義の警告判定は格納しない。</x:v>
+      </x:c>
+      <x:c r="K24" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L24" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="63" customHeight="1">
+      <x:c r="A25" s="165" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C25" s="166" t="str">
+        <x:v>OS 移行期間中</x:v>
+      </x:c>
+      <x:c r="D25" s="166" t="str">
+        <x:v>OS 名</x:v>
+      </x:c>
+      <x:c r="E25" s="166" t="str">
+        <x:v>Caption0 / Name0（候補）</x:v>
+      </x:c>
+      <x:c r="F25" s="166" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G25" s="166" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H25" s="166" t="str">
+        <x:v>os</x:v>
+      </x:c>
+      <x:c r="I25" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J25" s="166" t="str">
+        <x:v>ServiceNow 公式ターゲットクラス資料に cmdb_ci_computer.os が明記されている。</x:v>
+      </x:c>
+      <x:c r="K25" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L25" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="63" customHeight="1">
+      <x:c r="A26" s="165" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B26" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C26" s="166" t="str">
+        <x:v>OS 移行期間中</x:v>
+      </x:c>
+      <x:c r="D26" s="166" t="str">
+        <x:v>OS バージョン</x:v>
+      </x:c>
+      <x:c r="E26" s="166" t="str">
+        <x:v>Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F26" s="166" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G26" s="166" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H26" s="166" t="str">
+        <x:v>os_version</x:v>
+      </x:c>
+      <x:c r="I26" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J26" s="166" t="str">
+        <x:v>ServiceNow 公式ターゲットクラス資料に cmdb_ci_computer.os_version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K26" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L26" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="63" customHeight="1">
+      <x:c r="A27" s="165" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B27" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C27" s="166" t="str">
+        <x:v>OS 移行期間中</x:v>
+      </x:c>
+      <x:c r="D27" s="166" t="str">
+        <x:v>OS Service Pack</x:v>
+      </x:c>
+      <x:c r="E27" s="166" t="str">
+        <x:v>CSDVersion0 / ServicePackMajorVersion0（候補）</x:v>
+      </x:c>
+      <x:c r="F27" s="166" t="str">
+        <x:v>v_GS_OPERATING_SYSTEM</x:v>
+      </x:c>
+      <x:c r="G27" s="166" t="str">
+        <x:v>cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="H27" s="166" t="str">
+        <x:v>os_service_pack</x:v>
+      </x:c>
+      <x:c r="I27" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J27" s="166" t="str">
+        <x:v>標準ターゲット項目は存在する。実際の MECM 列名と変換内容は IntegrationHub ETL Data Map で確認する。</x:v>
+      </x:c>
+      <x:c r="K27" s="166" t="str">
+        <x:v>公式サポート・マッピング要確認</x:v>
+      </x:c>
+      <x:c r="L27" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="63" customHeight="1">
+      <x:c r="A28" s="165" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B28" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C28" s="166" t="str">
+        <x:v>OS 移行期間中</x:v>
+      </x:c>
+      <x:c r="D28" s="166" t="str">
+        <x:v>ライフサイクル段階</x:v>
+      </x:c>
+      <x:c r="E28" s="166" t="str">
+        <x:v>顧客ライフサイクルマスタの Stage</x:v>
+      </x:c>
+      <x:c r="F28" s="166" t="str">
+        <x:v>MECM の原始インベントリ項目ではない</x:v>
+      </x:c>
+      <x:c r="G28" s="166" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H28" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I28" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J28" s="166" t="str">
+        <x:v>移行期間は顧客業務ルールによる判定であり、標準 SG-SCCM ターゲット項目ではない。</x:v>
+      </x:c>
+      <x:c r="K28" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L28" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="63" customHeight="1">
+      <x:c r="A29" s="165" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B29" s="166" t="str">
+        <x:v>OS ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C29" s="166" t="str">
+        <x:v>OS 移行期間中</x:v>
+      </x:c>
+      <x:c r="D29" s="166" t="str">
+        <x:v>移行期間判定結果</x:v>
+      </x:c>
+      <x:c r="E29" s="166" t="str">
+        <x:v>OS 名 / バージョンとライフサイクルマスタの照合結果</x:v>
+      </x:c>
+      <x:c r="F29" s="166" t="str">
+        <x:v>顧客ルールエンジン</x:v>
+      </x:c>
+      <x:c r="G29" s="166" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H29" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I29" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J29" s="166" t="str">
+        <x:v>監査上の発見事項として保存し、cmdb_ci_computer への直接追加は推奨しない。</x:v>
+      </x:c>
+      <x:c r="K29" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L29" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="63" customHeight="1">
+      <x:c r="A30" s="99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B30" s="98" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C30" s="98" t="str">
+        <x:v>Windows パッチ未適用（公開後、翌々週以降）</x:v>
+      </x:c>
+      <x:c r="D30" s="98" t="str">
+        <x:v>KB / Article ID</x:v>
+      </x:c>
+      <x:c r="E30" s="98" t="str">
+        <x:v>ArticleID</x:v>
+      </x:c>
+      <x:c r="F30" s="98" t="str">
+        <x:v>v_UpdateInfo / v_UpdateCIs</x:v>
+      </x:c>
+      <x:c r="G30" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H30" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I30" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J30" s="98" t="str">
+        <x:v>MECM は更新メタデータを提供できるが、ServiceNow 公式 SG-SCCM ターゲット項目にはパッチ準拠明細が含まれない。</x:v>
+      </x:c>
+      <x:c r="K30" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L30" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="63" customHeight="1">
+      <x:c r="A31" s="99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B31" s="98" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C31" s="98" t="str">
+        <x:v>Windows パッチ未適用（公開後、翌々週以降）</x:v>
+      </x:c>
+      <x:c r="D31" s="98" t="str">
+        <x:v>パッチタイトル</x:v>
+      </x:c>
+      <x:c r="E31" s="98" t="str">
+        <x:v>Title</x:v>
+      </x:c>
+      <x:c r="F31" s="98" t="str">
+        <x:v>v_UpdateInfo</x:v>
+      </x:c>
+      <x:c r="G31" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H31" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I31" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J31" s="98" t="str">
+        <x:v>カスタム連携でパッチ準拠テーブルへ取り込めるが、標準 Connector では CMDB 項目へ直接格納できない。</x:v>
+      </x:c>
+      <x:c r="K31" s="98" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L31" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="63" customHeight="1">
+      <x:c r="A32" s="99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B32" s="98" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C32" s="98" t="str">
+        <x:v>Windows パッチ未適用（公開後、翌々週以降）</x:v>
+      </x:c>
+      <x:c r="D32" s="98" t="str">
+        <x:v>パッチ公開日</x:v>
+      </x:c>
+      <x:c r="E32" s="98" t="str">
+        <x:v>DateCreated / DatePosted（候補）</x:v>
+      </x:c>
+      <x:c r="F32" s="98" t="str">
+        <x:v>v_UpdateInfo / v_UpdateCIs</x:v>
+      </x:c>
+      <x:c r="G32" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H32" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I32" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J32" s="98" t="str">
+        <x:v>MECM には更新日情報があるが、標準 SG-SCCM ターゲットマッピングの対象外である。</x:v>
+      </x:c>
+      <x:c r="K32" s="98" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L32" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="63" customHeight="1">
+      <x:c r="A33" s="99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B33" s="98" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C33" s="98" t="str">
+        <x:v>Windows パッチ未適用（公開後、翌々週以降）</x:v>
+      </x:c>
+      <x:c r="D33" s="98" t="str">
+        <x:v>パッチ重要度</x:v>
+      </x:c>
+      <x:c r="E33" s="98" t="str">
+        <x:v>Severity</x:v>
+      </x:c>
+      <x:c r="F33" s="98" t="str">
+        <x:v>v_UpdateInfo / v_UpdateCIs</x:v>
+      </x:c>
+      <x:c r="G33" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H33" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I33" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J33" s="98" t="str">
+        <x:v>MECM には重要度情報があるが、標準 SG-SCCM ターゲットマッピングの対象外である。</x:v>
+      </x:c>
+      <x:c r="K33" s="98" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L33" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="63" customHeight="1">
+      <x:c r="A34" s="99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B34" s="98" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C34" s="98" t="str">
+        <x:v>Windows パッチ未適用（公開後、翌々週以降）</x:v>
+      </x:c>
+      <x:c r="D34" s="98" t="str">
+        <x:v>端末のパッチ準拠 / 検出状態</x:v>
+      </x:c>
+      <x:c r="E34" s="98" t="str">
+        <x:v>Status / Detection State</x:v>
+      </x:c>
+      <x:c r="F34" s="98" t="str">
+        <x:v>v_Update_ComplianceStatus / v_UpdateState_Combined</x:v>
+      </x:c>
+      <x:c r="G34" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H34" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I34" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J34" s="98" t="str">
+        <x:v>端末とパッチ間の多対多の準拠結果であり、単一の Computer CI 項目には格納できない。</x:v>
+      </x:c>
+      <x:c r="K34" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L34" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="63" customHeight="1">
+      <x:c r="A35" s="99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B35" s="98" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C35" s="98" t="str">
+        <x:v>Windows パッチ未適用（公開後、翌々週以降）</x:v>
+      </x:c>
+      <x:c r="D35" s="98" t="str">
+        <x:v>最終ステータス確認日時</x:v>
+      </x:c>
+      <x:c r="E35" s="98" t="str">
+        <x:v>LastStatusCheckTime</x:v>
+      </x:c>
+      <x:c r="F35" s="98" t="str">
+        <x:v>v_Update_ComplianceStatus</x:v>
+      </x:c>
+      <x:c r="G35" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H35" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I35" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J35" s="98" t="str">
+        <x:v>パッチ準拠イベントの日時であり、標準 CMDB の資産属性ではない。</x:v>
+      </x:c>
+      <x:c r="K35" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L35" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="63" customHeight="1">
+      <x:c r="A36" s="99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B36" s="98" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C36" s="98" t="str">
+        <x:v>Windows パッチ未適用（公開後、翌々週以降）</x:v>
+      </x:c>
+      <x:c r="D36" s="98" t="str">
+        <x:v>最終更新スキャン日時</x:v>
+      </x:c>
+      <x:c r="E36" s="98" t="str">
+        <x:v>LastScanTime</x:v>
+      </x:c>
+      <x:c r="F36" s="98" t="str">
+        <x:v>v_UpdateScanStatus</x:v>
+      </x:c>
+      <x:c r="G36" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H36" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I36" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J36" s="98" t="str">
+        <x:v>MECM には当該情報があるが、SG-SCCM の標準ターゲット項目に Windows Update スキャン日時は含まれない。</x:v>
+      </x:c>
+      <x:c r="K36" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L36" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="63" customHeight="1">
+      <x:c r="A37" s="99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B37" s="98" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C37" s="98" t="str">
+        <x:v>Windows パッチ未適用（公開後、翌々週以降）</x:v>
+      </x:c>
+      <x:c r="D37" s="98" t="str">
+        <x:v>未適用日数 / 週数および最終判定</x:v>
+      </x:c>
+      <x:c r="E37" s="98" t="str">
+        <x:v>判定日 - パッチ公開日（Compliance Status と組み合わせ）</x:v>
+      </x:c>
+      <x:c r="F37" s="98" t="str">
+        <x:v>算出項目</x:v>
+      </x:c>
+      <x:c r="G37" s="98" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H37" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I37" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J37" s="98" t="str">
+        <x:v>公開翌週 / 翌々週のルールは顧客監査ロジックであり、カスタム準拠結果として保存する。</x:v>
+      </x:c>
+      <x:c r="K37" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L37" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="63" customHeight="1">
+      <x:c r="A38" s="165" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B38" s="166" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C38" s="166" t="str">
+        <x:v>Windows パッチ未適用（公開翌週）</x:v>
+      </x:c>
+      <x:c r="D38" s="166" t="str">
+        <x:v>KB / Article ID</x:v>
+      </x:c>
+      <x:c r="E38" s="166" t="str">
+        <x:v>ArticleID</x:v>
+      </x:c>
+      <x:c r="F38" s="166" t="str">
+        <x:v>v_UpdateInfo / v_UpdateCIs</x:v>
+      </x:c>
+      <x:c r="G38" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H38" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I38" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J38" s="166" t="str">
+        <x:v>MECM は更新メタデータを提供できるが、ServiceNow 公式 SG-SCCM ターゲット項目にはパッチ準拠明細が含まれない。</x:v>
+      </x:c>
+      <x:c r="K38" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L38" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="63" customHeight="1">
+      <x:c r="A39" s="165" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B39" s="166" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C39" s="166" t="str">
+        <x:v>Windows パッチ未適用（公開翌週）</x:v>
+      </x:c>
+      <x:c r="D39" s="166" t="str">
+        <x:v>パッチタイトル</x:v>
+      </x:c>
+      <x:c r="E39" s="166" t="str">
+        <x:v>Title</x:v>
+      </x:c>
+      <x:c r="F39" s="166" t="str">
+        <x:v>v_UpdateInfo</x:v>
+      </x:c>
+      <x:c r="G39" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H39" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I39" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J39" s="166" t="str">
+        <x:v>カスタム連携でパッチ準拠テーブルへ取り込めるが、標準 Connector では CMDB 項目へ直接格納できない。</x:v>
+      </x:c>
+      <x:c r="K39" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L39" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="63" customHeight="1">
+      <x:c r="A40" s="165" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B40" s="166" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C40" s="166" t="str">
+        <x:v>Windows パッチ未適用（公開翌週）</x:v>
+      </x:c>
+      <x:c r="D40" s="166" t="str">
+        <x:v>パッチ公開日</x:v>
+      </x:c>
+      <x:c r="E40" s="166" t="str">
+        <x:v>DateCreated / DatePosted（候補）</x:v>
+      </x:c>
+      <x:c r="F40" s="166" t="str">
+        <x:v>v_UpdateInfo / v_UpdateCIs</x:v>
+      </x:c>
+      <x:c r="G40" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H40" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I40" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J40" s="166" t="str">
+        <x:v>MECM には更新日情報があるが、標準 SG-SCCM ターゲットマッピングの対象外である。</x:v>
+      </x:c>
+      <x:c r="K40" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L40" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="63" customHeight="1">
+      <x:c r="A41" s="165" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B41" s="166" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C41" s="166" t="str">
+        <x:v>Windows パッチ未適用（公開翌週）</x:v>
+      </x:c>
+      <x:c r="D41" s="166" t="str">
+        <x:v>パッチ重要度</x:v>
+      </x:c>
+      <x:c r="E41" s="166" t="str">
+        <x:v>Severity</x:v>
+      </x:c>
+      <x:c r="F41" s="166" t="str">
+        <x:v>v_UpdateInfo / v_UpdateCIs</x:v>
+      </x:c>
+      <x:c r="G41" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H41" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I41" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J41" s="166" t="str">
+        <x:v>MECM には重要度情報があるが、標準 SG-SCCM ターゲットマッピングの対象外である。</x:v>
+      </x:c>
+      <x:c r="K41" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L41" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="63" customHeight="1">
+      <x:c r="A42" s="165" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B42" s="166" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C42" s="166" t="str">
+        <x:v>Windows パッチ未適用（公開翌週）</x:v>
+      </x:c>
+      <x:c r="D42" s="166" t="str">
+        <x:v>端末のパッチ準拠 / 検出状態</x:v>
+      </x:c>
+      <x:c r="E42" s="166" t="str">
+        <x:v>Status / Detection State</x:v>
+      </x:c>
+      <x:c r="F42" s="166" t="str">
+        <x:v>v_Update_ComplianceStatus / v_UpdateState_Combined</x:v>
+      </x:c>
+      <x:c r="G42" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H42" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I42" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J42" s="166" t="str">
+        <x:v>端末とパッチ間の多対多の準拠結果であり、単一の Computer CI 項目には格納できない。</x:v>
+      </x:c>
+      <x:c r="K42" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L42" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="63" customHeight="1">
+      <x:c r="A43" s="165" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B43" s="166" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C43" s="166" t="str">
+        <x:v>Windows パッチ未適用（公開翌週）</x:v>
+      </x:c>
+      <x:c r="D43" s="166" t="str">
+        <x:v>最終ステータス確認日時</x:v>
+      </x:c>
+      <x:c r="E43" s="166" t="str">
+        <x:v>LastStatusCheckTime</x:v>
+      </x:c>
+      <x:c r="F43" s="166" t="str">
+        <x:v>v_Update_ComplianceStatus</x:v>
+      </x:c>
+      <x:c r="G43" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H43" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I43" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J43" s="166" t="str">
+        <x:v>パッチ準拠イベントの日時であり、標準 CMDB の資産属性ではない。</x:v>
+      </x:c>
+      <x:c r="K43" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L43" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="63" customHeight="1">
+      <x:c r="A44" s="165" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B44" s="166" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C44" s="166" t="str">
+        <x:v>Windows パッチ未適用（公開翌週）</x:v>
+      </x:c>
+      <x:c r="D44" s="166" t="str">
+        <x:v>最終更新スキャン日時</x:v>
+      </x:c>
+      <x:c r="E44" s="166" t="str">
+        <x:v>LastScanTime</x:v>
+      </x:c>
+      <x:c r="F44" s="166" t="str">
+        <x:v>v_UpdateScanStatus</x:v>
+      </x:c>
+      <x:c r="G44" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H44" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I44" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J44" s="166" t="str">
+        <x:v>MECM には当該情報があるが、SG-SCCM の標準ターゲット項目に Windows Update スキャン日時は含まれない。</x:v>
+      </x:c>
+      <x:c r="K44" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L44" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="63" customHeight="1">
+      <x:c r="A45" s="165" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B45" s="166" t="str">
+        <x:v>Windows パッチ</x:v>
+      </x:c>
+      <x:c r="C45" s="166" t="str">
+        <x:v>Windows パッチ未適用（公開翌週）</x:v>
+      </x:c>
+      <x:c r="D45" s="166" t="str">
+        <x:v>未適用日数 / 週数および最終判定</x:v>
+      </x:c>
+      <x:c r="E45" s="166" t="str">
+        <x:v>判定日 - パッチ公開日（Compliance Status と組み合わせ）</x:v>
+      </x:c>
+      <x:c r="F45" s="166" t="str">
+        <x:v>算出項目</x:v>
+      </x:c>
+      <x:c r="G45" s="166" t="str">
+        <x:v>標準 CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H45" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I45" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J45" s="166" t="str">
+        <x:v>公開翌週 / 翌々週のルールは顧客監査ロジックであり、カスタム準拠結果として保存する。</x:v>
+      </x:c>
+      <x:c r="K45" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L45" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="63" customHeight="1">
+      <x:c r="A46" s="99" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B46" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C46" s="98" t="str">
+        <x:v>GUEST アカウント有効</x:v>
+      </x:c>
+      <x:c r="D46" s="98" t="str">
+        <x:v>アカウント名</x:v>
+      </x:c>
+      <x:c r="E46" s="98" t="str">
+        <x:v>Name0</x:v>
+      </x:c>
+      <x:c r="F46" s="98" t="str">
+        <x:v>v_GS_SYSTEM_ACCOUNT</x:v>
+      </x:c>
+      <x:c r="G46" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H46" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I46" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J46" s="98" t="str">
+        <x:v>MECM のインベントリまたは Compliance Baseline で取得できるが、公式 SG-SCCM ターゲット項目にローカルアカウント設定はない。</x:v>
+      </x:c>
+      <x:c r="K46" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L46" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="63" customHeight="1">
+      <x:c r="A47" s="99" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B47" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C47" s="98" t="str">
+        <x:v>GUEST アカウント有効</x:v>
+      </x:c>
+      <x:c r="D47" s="98" t="str">
+        <x:v>アカウント SID</x:v>
+      </x:c>
+      <x:c r="E47" s="98" t="str">
+        <x:v>SID0</x:v>
+      </x:c>
+      <x:c r="F47" s="98" t="str">
+        <x:v>v_GS_SYSTEM_ACCOUNT</x:v>
+      </x:c>
+      <x:c r="G47" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H47" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I47" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J47" s="98" t="str">
+        <x:v>MECM のインベントリまたは Compliance Baseline で取得できるが、公式 SG-SCCM ターゲット項目にローカルアカウント設定はない。</x:v>
+      </x:c>
+      <x:c r="K47" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L47" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="63" customHeight="1">
+      <x:c r="A48" s="99" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B48" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C48" s="98" t="str">
+        <x:v>GUEST アカウント有効</x:v>
+      </x:c>
+      <x:c r="D48" s="98" t="str">
+        <x:v>アカウントの有効 / 無効</x:v>
+      </x:c>
+      <x:c r="E48" s="98" t="str">
+        <x:v>Disabled0 / Enabled（候補）</x:v>
+      </x:c>
+      <x:c r="F48" s="98" t="str">
+        <x:v>v_GS_SYSTEM_ACCOUNT / Compliance Baseline</x:v>
+      </x:c>
+      <x:c r="G48" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H48" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I48" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J48" s="98" t="str">
+        <x:v>MECM のインベントリまたは Compliance Baseline で取得できるが、公式 SG-SCCM ターゲット項目にローカルアカウント設定はない。</x:v>
+      </x:c>
+      <x:c r="K48" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L48" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="63" customHeight="1">
+      <x:c r="A49" s="99" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B49" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C49" s="98" t="str">
+        <x:v>GUEST アカウント有効</x:v>
+      </x:c>
+      <x:c r="D49" s="98" t="str">
+        <x:v>ローカル / ドメインアカウント属性</x:v>
+      </x:c>
+      <x:c r="E49" s="98" t="str">
+        <x:v>Domain0 / LocalAccount0（候補）</x:v>
+      </x:c>
+      <x:c r="F49" s="98" t="str">
+        <x:v>v_GS_SYSTEM_ACCOUNT</x:v>
+      </x:c>
+      <x:c r="G49" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H49" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I49" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J49" s="98" t="str">
+        <x:v>MECM のインベントリまたは Compliance Baseline で取得できるが、公式 SG-SCCM ターゲット項目にローカルアカウント設定はない。</x:v>
+      </x:c>
+      <x:c r="K49" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L49" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="63" customHeight="1">
+      <x:c r="A50" s="99" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B50" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C50" s="98" t="str">
+        <x:v>GUEST アカウント有効</x:v>
+      </x:c>
+      <x:c r="D50" s="98" t="str">
+        <x:v>Guest 有効判定</x:v>
+      </x:c>
+      <x:c r="E50" s="98" t="str">
+        <x:v>Name='Guest' かつ Enabled=true</x:v>
+      </x:c>
+      <x:c r="F50" s="98" t="str">
+        <x:v>算出項目</x:v>
+      </x:c>
+      <x:c r="G50" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H50" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I50" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J50" s="98" t="str">
+        <x:v>MECM のインベントリまたは Compliance Baseline で取得できるが、公式 SG-SCCM ターゲット項目にローカルアカウント設定はない。</x:v>
+      </x:c>
+      <x:c r="K50" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L50" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="63" customHeight="1">
+      <x:c r="A51" s="165" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B51" s="166" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C51" s="166" t="str">
+        <x:v>自動ログオン設定有効</x:v>
+      </x:c>
+      <x:c r="D51" s="166" t="str">
+        <x:v>AutoAdminLogon 値</x:v>
+      </x:c>
+      <x:c r="E51" s="166" t="str">
+        <x:v>AutoAdminLogon</x:v>
+      </x:c>
+      <x:c r="F51" s="166" t="str">
+        <x:v>カスタムレジストリインベントリ / Compliance Baseline</x:v>
+      </x:c>
+      <x:c r="G51" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H51" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I51" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J51" s="166" t="str">
+        <x:v>レジストリ / ポリシーの準拠情報である。標準 Connector は任意のレジストリ値を CMDB 項目へ自動マッピングしない。</x:v>
+      </x:c>
+      <x:c r="K51" s="166" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L51" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="63" customHeight="1">
+      <x:c r="A52" s="165" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B52" s="166" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C52" s="166" t="str">
+        <x:v>自動ログオン設定有効</x:v>
+      </x:c>
+      <x:c r="D52" s="166" t="str">
+        <x:v>DefaultUserName</x:v>
+      </x:c>
+      <x:c r="E52" s="166" t="str">
+        <x:v>DefaultUserName</x:v>
+      </x:c>
+      <x:c r="F52" s="166" t="str">
+        <x:v>カスタムレジストリインベントリ / Compliance Baseline</x:v>
+      </x:c>
+      <x:c r="G52" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H52" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I52" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J52" s="166" t="str">
+        <x:v>レジストリ / ポリシーの準拠情報である。標準 Connector は任意のレジストリ値を CMDB 項目へ自動マッピングしない。</x:v>
+      </x:c>
+      <x:c r="K52" s="166" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L52" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="63" customHeight="1">
+      <x:c r="A53" s="165" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B53" s="166" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C53" s="166" t="str">
+        <x:v>自動ログオン設定有効</x:v>
+      </x:c>
+      <x:c r="D53" s="166" t="str">
+        <x:v>レジストリパス</x:v>
+      </x:c>
+      <x:c r="E53" s="166" t="str">
+        <x:v>RegistryKey / RegistryPath（候補）</x:v>
+      </x:c>
+      <x:c r="F53" s="166" t="str">
+        <x:v>カスタムレジストリインベントリ</x:v>
+      </x:c>
+      <x:c r="G53" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H53" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I53" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J53" s="166" t="str">
+        <x:v>レジストリ / ポリシーの準拠情報である。標準 Connector は任意のレジストリ値を CMDB 項目へ自動マッピングしない。</x:v>
+      </x:c>
+      <x:c r="K53" s="166" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L53" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="63" customHeight="1">
+      <x:c r="A54" s="165" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B54" s="166" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C54" s="166" t="str">
+        <x:v>自動ログオン設定有効</x:v>
+      </x:c>
+      <x:c r="D54" s="166" t="str">
+        <x:v>自動ログオン有効判定</x:v>
+      </x:c>
+      <x:c r="E54" s="166" t="str">
+        <x:v>AutoAdminLogon='1'</x:v>
+      </x:c>
+      <x:c r="F54" s="166" t="str">
+        <x:v>算出項目</x:v>
+      </x:c>
+      <x:c r="G54" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H54" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I54" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J54" s="166" t="str">
+        <x:v>レジストリ / ポリシーの準拠情報である。標準 Connector は任意のレジストリ値を CMDB 項目へ自動マッピングしない。</x:v>
+      </x:c>
+      <x:c r="K54" s="166" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L54" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="63" customHeight="1">
+      <x:c r="A55" s="99" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B55" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C55" s="98" t="str">
+        <x:v>スクリーンセーバーのパスワード保護無効</x:v>
+      </x:c>
+      <x:c r="D55" s="98" t="str">
+        <x:v>スクリーンセーバーの有効 / 無効</x:v>
+      </x:c>
+      <x:c r="E55" s="98" t="str">
+        <x:v>ScreenSaveActive / Policy Result（候補）</x:v>
+      </x:c>
+      <x:c r="F55" s="98" t="str">
+        <x:v>カスタムレジストリインベントリ / Compliance Baseline / v_GS_DESKTOP</x:v>
+      </x:c>
+      <x:c r="G55" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H55" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I55" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J55" s="98" t="str">
+        <x:v>セキュリティポリシーの状態であり、標準 Computer CI 項目ではない。</x:v>
+      </x:c>
+      <x:c r="K55" s="98" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L55" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="63" customHeight="1">
+      <x:c r="A56" s="99" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B56" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C56" s="98" t="str">
+        <x:v>スクリーンセーバーのパスワード保護無効</x:v>
+      </x:c>
+      <x:c r="D56" s="98" t="str">
+        <x:v>パスワード保護の有効 / 無効</x:v>
+      </x:c>
+      <x:c r="E56" s="98" t="str">
+        <x:v>ScreenSaverIsSecure / ScreenSaverSecure（候補）</x:v>
+      </x:c>
+      <x:c r="F56" s="98" t="str">
+        <x:v>カスタムレジストリインベントリ / Compliance Baseline / v_GS_DESKTOP</x:v>
+      </x:c>
+      <x:c r="G56" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H56" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I56" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J56" s="98" t="str">
+        <x:v>セキュリティポリシーの状態であり、標準 Computer CI 項目ではない。</x:v>
+      </x:c>
+      <x:c r="K56" s="98" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L56" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="63" customHeight="1">
+      <x:c r="A57" s="99" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B57" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C57" s="98" t="str">
+        <x:v>スクリーンセーバーのパスワード保護無効</x:v>
+      </x:c>
+      <x:c r="D57" s="98" t="str">
+        <x:v>スクリーンセーバーのタイムアウト</x:v>
+      </x:c>
+      <x:c r="E57" s="98" t="str">
+        <x:v>ScreenSaveTimeOut（候補）</x:v>
+      </x:c>
+      <x:c r="F57" s="98" t="str">
+        <x:v>カスタムレジストリインベントリ / Compliance Baseline / v_GS_DESKTOP</x:v>
+      </x:c>
+      <x:c r="G57" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H57" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I57" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J57" s="98" t="str">
+        <x:v>セキュリティポリシーの状態であり、標準 Computer CI 項目ではない。</x:v>
+      </x:c>
+      <x:c r="K57" s="98" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L57" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="63" customHeight="1">
+      <x:c r="A58" s="99" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B58" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C58" s="98" t="str">
+        <x:v>スクリーンセーバーのパスワード保護無効</x:v>
+      </x:c>
+      <x:c r="D58" s="98" t="str">
+        <x:v>ポリシー / レジストリパス</x:v>
+      </x:c>
+      <x:c r="E58" s="98" t="str">
+        <x:v>PolicyPath / RegistryPath（候補）</x:v>
+      </x:c>
+      <x:c r="F58" s="98" t="str">
+        <x:v>カスタムレジストリインベントリ / Compliance Baseline / v_GS_DESKTOP</x:v>
+      </x:c>
+      <x:c r="G58" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H58" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I58" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J58" s="98" t="str">
+        <x:v>セキュリティポリシーの状態であり、標準 Computer CI 項目ではない。</x:v>
+      </x:c>
+      <x:c r="K58" s="98" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L58" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="63" customHeight="1">
+      <x:c r="A59" s="99" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B59" s="98" t="str">
+        <x:v>ローカルセキュリティ設定</x:v>
+      </x:c>
+      <x:c r="C59" s="98" t="str">
+        <x:v>スクリーンセーバーのパスワード保護無効</x:v>
+      </x:c>
+      <x:c r="D59" s="98" t="str">
+        <x:v>スクリーンセーバーのパスワード保護無効判定</x:v>
+      </x:c>
+      <x:c r="E59" s="98" t="str">
+        <x:v>有効状態 + パスワード保護 + タイムアウトルール</x:v>
+      </x:c>
+      <x:c r="F59" s="98" t="str">
+        <x:v>カスタムレジストリインベントリ / Compliance Baseline / v_GS_DESKTOP</x:v>
+      </x:c>
+      <x:c r="G59" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H59" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I59" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J59" s="98" t="str">
+        <x:v>セキュリティポリシーの状態であり、標準 Computer CI 項目ではない。</x:v>
+      </x:c>
+      <x:c r="K59" s="98" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L59" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="63" customHeight="1">
+      <x:c r="A60" s="165" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B60" s="166" t="str">
+        <x:v>Windows Update 設定</x:v>
+      </x:c>
+      <x:c r="C60" s="166" t="str">
+        <x:v>Windows 自動更新無効</x:v>
+      </x:c>
+      <x:c r="D60" s="166" t="str">
+        <x:v>Windows Update 自動更新ポリシー</x:v>
+      </x:c>
+      <x:c r="E60" s="166" t="str">
+        <x:v>AUOptions / NoAutoUpdate（候補）</x:v>
+      </x:c>
+      <x:c r="F60" s="166" t="str">
+        <x:v>カスタムレジストリインベントリ / Compliance Baseline</x:v>
+      </x:c>
+      <x:c r="G60" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H60" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I60" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J60" s="166" t="str">
+        <x:v>MECM の更新 View で一部情報を取得できるが、標準 SG-SCCM ターゲットマッピングに該当項目はない。</x:v>
+      </x:c>
+      <x:c r="K60" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L60" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="63" customHeight="1">
+      <x:c r="A61" s="165" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B61" s="166" t="str">
+        <x:v>Windows Update 設定</x:v>
+      </x:c>
+      <x:c r="C61" s="166" t="str">
+        <x:v>Windows 自動更新無効</x:v>
+      </x:c>
+      <x:c r="D61" s="166" t="str">
+        <x:v>最終更新スキャン状態</x:v>
+      </x:c>
+      <x:c r="E61" s="166" t="str">
+        <x:v>LastScanState</x:v>
+      </x:c>
+      <x:c r="F61" s="166" t="str">
+        <x:v>v_UpdateScanStatus</x:v>
+      </x:c>
+      <x:c r="G61" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H61" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I61" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J61" s="166" t="str">
+        <x:v>MECM の更新 View で一部情報を取得できるが、標準 SG-SCCM ターゲットマッピングに該当項目はない。</x:v>
+      </x:c>
+      <x:c r="K61" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L61" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="63" customHeight="1">
+      <x:c r="A62" s="165" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B62" s="166" t="str">
+        <x:v>Windows Update 設定</x:v>
+      </x:c>
+      <x:c r="C62" s="166" t="str">
+        <x:v>Windows 自動更新無効</x:v>
+      </x:c>
+      <x:c r="D62" s="166" t="str">
+        <x:v>最終更新スキャン日時</x:v>
+      </x:c>
+      <x:c r="E62" s="166" t="str">
+        <x:v>LastScanTime</x:v>
+      </x:c>
+      <x:c r="F62" s="166" t="str">
+        <x:v>v_UpdateScanStatus</x:v>
+      </x:c>
+      <x:c r="G62" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H62" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I62" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J62" s="166" t="str">
+        <x:v>MECM の更新 View で一部情報を取得できるが、標準 SG-SCCM ターゲットマッピングに該当項目はない。</x:v>
+      </x:c>
+      <x:c r="K62" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L62" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="63" customHeight="1">
+      <x:c r="A63" s="165" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B63" s="166" t="str">
+        <x:v>Windows Update 設定</x:v>
+      </x:c>
+      <x:c r="C63" s="166" t="str">
+        <x:v>Windows 自動更新無効</x:v>
+      </x:c>
+      <x:c r="D63" s="166" t="str">
+        <x:v>最終スキャンエラーコード</x:v>
+      </x:c>
+      <x:c r="E63" s="166" t="str">
+        <x:v>LastErrorCode</x:v>
+      </x:c>
+      <x:c r="F63" s="166" t="str">
+        <x:v>v_UpdateScanStatus</x:v>
+      </x:c>
+      <x:c r="G63" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H63" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I63" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J63" s="166" t="str">
+        <x:v>MECM の更新 View で一部情報を取得できるが、標準 SG-SCCM ターゲットマッピングに該当項目はない。</x:v>
+      </x:c>
+      <x:c r="K63" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L63" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="63" customHeight="1">
+      <x:c r="A64" s="165" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B64" s="166" t="str">
+        <x:v>Windows Update 設定</x:v>
+      </x:c>
+      <x:c r="C64" s="166" t="str">
+        <x:v>Windows 自動更新無効</x:v>
+      </x:c>
+      <x:c r="D64" s="166" t="str">
+        <x:v>Windows Update Agent バージョン</x:v>
+      </x:c>
+      <x:c r="E64" s="166" t="str">
+        <x:v>LastWUAVersion</x:v>
+      </x:c>
+      <x:c r="F64" s="166" t="str">
+        <x:v>v_UpdateScanStatus</x:v>
+      </x:c>
+      <x:c r="G64" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H64" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I64" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J64" s="166" t="str">
+        <x:v>MECM の更新 View で一部情報を取得できるが、標準 SG-SCCM ターゲットマッピングに該当項目はない。</x:v>
+      </x:c>
+      <x:c r="K64" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L64" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="63" customHeight="1">
+      <x:c r="A65" s="165" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B65" s="166" t="str">
+        <x:v>Windows Update 設定</x:v>
+      </x:c>
+      <x:c r="C65" s="166" t="str">
+        <x:v>Windows 自動更新無効</x:v>
+      </x:c>
+      <x:c r="D65" s="166" t="str">
+        <x:v>自動更新無効判定</x:v>
+      </x:c>
+      <x:c r="E65" s="166" t="str">
+        <x:v>ポリシー値 + スキャン状態の判定結果</x:v>
+      </x:c>
+      <x:c r="F65" s="166" t="str">
+        <x:v>算出項目</x:v>
+      </x:c>
+      <x:c r="G65" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H65" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I65" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J65" s="166" t="str">
+        <x:v>MECM の更新 View で一部情報を取得できるが、標準 SG-SCCM ターゲットマッピングに該当項目はない。</x:v>
+      </x:c>
+      <x:c r="K65" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L65" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/software-updates-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="63" customHeight="1">
+      <x:c r="A66" s="99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B66" s="98" t="str">
+        <x:v>Windows Service</x:v>
+      </x:c>
+      <x:c r="C66" s="98" t="str">
+        <x:v>不要なサービスが実行中</x:v>
+      </x:c>
+      <x:c r="D66" s="98" t="str">
+        <x:v>Windows Service 名</x:v>
+      </x:c>
+      <x:c r="E66" s="98" t="str">
+        <x:v>Name0</x:v>
+      </x:c>
+      <x:c r="F66" s="98" t="str">
+        <x:v>v_GS_SERVICE</x:v>
+      </x:c>
+      <x:c r="G66" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H66" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I66" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J66" s="98" t="str">
+        <x:v>MECM は Windows Service を収集できるが、ServiceNow 公式 SG-SCCM ターゲットクラスに Windows Service インベントリは含まれない。cmdb_ci_service には格納しない。</x:v>
+      </x:c>
+      <x:c r="K66" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L66" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="63" customHeight="1">
+      <x:c r="A67" s="99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B67" s="98" t="str">
+        <x:v>Windows Service</x:v>
+      </x:c>
+      <x:c r="C67" s="98" t="str">
+        <x:v>不要なサービスが実行中</x:v>
+      </x:c>
+      <x:c r="D67" s="98" t="str">
+        <x:v>表示名</x:v>
+      </x:c>
+      <x:c r="E67" s="98" t="str">
+        <x:v>DisplayName0</x:v>
+      </x:c>
+      <x:c r="F67" s="98" t="str">
+        <x:v>v_GS_SERVICE</x:v>
+      </x:c>
+      <x:c r="G67" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H67" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I67" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J67" s="98" t="str">
+        <x:v>MECM は Windows Service を収集できるが、ServiceNow 公式 SG-SCCM ターゲットクラスに Windows Service インベントリは含まれない。cmdb_ci_service には格納しない。</x:v>
+      </x:c>
+      <x:c r="K67" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L67" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="63" customHeight="1">
+      <x:c r="A68" s="99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B68" s="98" t="str">
+        <x:v>Windows Service</x:v>
+      </x:c>
+      <x:c r="C68" s="98" t="str">
+        <x:v>不要なサービスが実行中</x:v>
+      </x:c>
+      <x:c r="D68" s="98" t="str">
+        <x:v>実行状態</x:v>
+      </x:c>
+      <x:c r="E68" s="98" t="str">
+        <x:v>State0</x:v>
+      </x:c>
+      <x:c r="F68" s="98" t="str">
+        <x:v>v_GS_SERVICE</x:v>
+      </x:c>
+      <x:c r="G68" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H68" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I68" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J68" s="98" t="str">
+        <x:v>MECM は Windows Service を収集できるが、ServiceNow 公式 SG-SCCM ターゲットクラスに Windows Service インベントリは含まれない。cmdb_ci_service には格納しない。</x:v>
+      </x:c>
+      <x:c r="K68" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L68" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="63" customHeight="1">
+      <x:c r="A69" s="99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B69" s="98" t="str">
+        <x:v>Windows Service</x:v>
+      </x:c>
+      <x:c r="C69" s="98" t="str">
+        <x:v>不要なサービスが実行中</x:v>
+      </x:c>
+      <x:c r="D69" s="98" t="str">
+        <x:v>起動種類</x:v>
+      </x:c>
+      <x:c r="E69" s="98" t="str">
+        <x:v>StartMode0</x:v>
+      </x:c>
+      <x:c r="F69" s="98" t="str">
+        <x:v>v_GS_SERVICE</x:v>
+      </x:c>
+      <x:c r="G69" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H69" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I69" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J69" s="98" t="str">
+        <x:v>MECM は Windows Service を収集できるが、ServiceNow 公式 SG-SCCM ターゲットクラスに Windows Service インベントリは含まれない。cmdb_ci_service には格納しない。</x:v>
+      </x:c>
+      <x:c r="K69" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L69" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="63" customHeight="1">
+      <x:c r="A70" s="99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B70" s="98" t="str">
+        <x:v>Windows Service</x:v>
+      </x:c>
+      <x:c r="C70" s="98" t="str">
+        <x:v>不要なサービスが実行中</x:v>
+      </x:c>
+      <x:c r="D70" s="98" t="str">
+        <x:v>実行ファイルパス</x:v>
+      </x:c>
+      <x:c r="E70" s="98" t="str">
+        <x:v>PathName0</x:v>
+      </x:c>
+      <x:c r="F70" s="98" t="str">
+        <x:v>v_GS_SERVICE</x:v>
+      </x:c>
+      <x:c r="G70" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H70" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I70" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J70" s="98" t="str">
+        <x:v>MECM は Windows Service を収集できるが、ServiceNow 公式 SG-SCCM ターゲットクラスに Windows Service インベントリは含まれない。cmdb_ci_service には格納しない。</x:v>
+      </x:c>
+      <x:c r="K70" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L70" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="63" customHeight="1">
+      <x:c r="A71" s="99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B71" s="98" t="str">
+        <x:v>Windows Service</x:v>
+      </x:c>
+      <x:c r="C71" s="98" t="str">
+        <x:v>不要なサービスが実行中</x:v>
+      </x:c>
+      <x:c r="D71" s="98" t="str">
+        <x:v>実行アカウント</x:v>
+      </x:c>
+      <x:c r="E71" s="98" t="str">
+        <x:v>StartName0</x:v>
+      </x:c>
+      <x:c r="F71" s="98" t="str">
+        <x:v>v_GS_SERVICE</x:v>
+      </x:c>
+      <x:c r="G71" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H71" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I71" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J71" s="98" t="str">
+        <x:v>MECM は Windows Service を収集できるが、ServiceNow 公式 SG-SCCM ターゲットクラスに Windows Service インベントリは含まれない。cmdb_ci_service には格納しない。</x:v>
+      </x:c>
+      <x:c r="K71" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L71" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="63" customHeight="1">
+      <x:c r="A72" s="99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B72" s="98" t="str">
+        <x:v>Windows Service</x:v>
+      </x:c>
+      <x:c r="C72" s="98" t="str">
+        <x:v>不要なサービスが実行中</x:v>
+      </x:c>
+      <x:c r="D72" s="98" t="str">
+        <x:v>不要サービス判定</x:v>
+      </x:c>
+      <x:c r="E72" s="98" t="str">
+        <x:v>サービスリスト照合 + State='Running'</x:v>
+      </x:c>
+      <x:c r="F72" s="98" t="str">
+        <x:v>v_GS_SERVICE</x:v>
+      </x:c>
+      <x:c r="G72" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H72" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I72" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J72" s="98" t="str">
+        <x:v>MECM は Windows Service を収集できるが、ServiceNow 公式 SG-SCCM ターゲットクラスに Windows Service インベントリは含まれない。cmdb_ci_service には格納しない。</x:v>
+      </x:c>
+      <x:c r="K72" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L72" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="63" customHeight="1">
+      <x:c r="A73" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B73" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C73" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D73" s="166" t="str">
+        <x:v>AV 製品名</x:v>
+      </x:c>
+      <x:c r="E73" s="166" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F73" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G73" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H73" s="166" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I73" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J73" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K73" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L73" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="63" customHeight="1">
+      <x:c r="A74" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B74" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C74" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D74" s="166" t="str">
+        <x:v>AV 製品バージョン</x:v>
+      </x:c>
+      <x:c r="E74" s="166" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F74" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G74" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H74" s="166" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I74" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J74" s="166" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K74" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L74" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="63" customHeight="1">
+      <x:c r="A75" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B75" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C75" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D75" s="166" t="str">
+        <x:v>AV 製品 Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E75" s="166" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F75" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G75" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H75" s="166" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I75" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J75" s="166" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K75" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L75" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="63" customHeight="1">
+      <x:c r="A76" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B76" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C76" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D76" s="166" t="str">
+        <x:v>AV 製品インストール日</x:v>
+      </x:c>
+      <x:c r="E76" s="166" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F76" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G76" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H76" s="166" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I76" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J76" s="166" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K76" s="166" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L76" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="63" customHeight="1">
+      <x:c r="A77" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B77" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C77" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D77" s="166" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E77" s="166" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F77" s="166" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G77" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H77" s="166" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I77" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J77" s="166" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K77" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L77" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="63" customHeight="1">
+      <x:c r="A78" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B78" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C78" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D78" s="166" t="str">
+        <x:v>AV / Antimalware の有効 / 無効</x:v>
+      </x:c>
+      <x:c r="E78" s="166" t="str">
+        <x:v>AntivirusEnabled / AntimalwareEnabled（候補）</x:v>
+      </x:c>
+      <x:c r="F78" s="166" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus</x:v>
+      </x:c>
+      <x:c r="G78" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H78" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I78" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J78" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できるが、AV ヘルス、指定製品、ライフサイクル判定は標準ターゲット項目ではない。</x:v>
+      </x:c>
+      <x:c r="K78" s="166" t="str">
+        <x:v>公式情報に基づく推定 / 顧客ルール</x:v>
+      </x:c>
+      <x:c r="L78" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="63" customHeight="1">
+      <x:c r="A79" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B79" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C79" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D79" s="166" t="str">
+        <x:v>Endpoint Protection の保護状態</x:v>
+      </x:c>
+      <x:c r="E79" s="166" t="str">
+        <x:v>Protected / AtRisk / Supported（候補）</x:v>
+      </x:c>
+      <x:c r="F79" s="166" t="str">
+        <x:v>v_EndpointProtectionStatus</x:v>
+      </x:c>
+      <x:c r="G79" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H79" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I79" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J79" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できるが、AV ヘルス、指定製品、ライフサイクル判定は標準ターゲット項目ではない。</x:v>
+      </x:c>
+      <x:c r="K79" s="166" t="str">
+        <x:v>公式情報に基づく推定 / 顧客ルール</x:v>
+      </x:c>
+      <x:c r="L79" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="63" customHeight="1">
+      <x:c r="A80" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B80" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C80" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D80" s="166" t="str">
+        <x:v>指定 AV 製品との照合結果</x:v>
+      </x:c>
+      <x:c r="E80" s="166" t="str">
+        <x:v>インストール製品と顧客指定 AV リストの比較結果</x:v>
+      </x:c>
+      <x:c r="F80" s="166" t="str">
+        <x:v>顧客ルールエンジン</x:v>
+      </x:c>
+      <x:c r="G80" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H80" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I80" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J80" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できるが、AV ヘルス、指定製品、ライフサイクル判定は標準ターゲット項目ではない。</x:v>
+      </x:c>
+      <x:c r="K80" s="166" t="str">
+        <x:v>公式情報に基づく推定 / 顧客ルール</x:v>
+      </x:c>
+      <x:c r="L80" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="63" customHeight="1">
+      <x:c r="A81" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B81" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C81" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D81" s="166" t="str">
+        <x:v>AV 製品サポート状態</x:v>
+      </x:c>
+      <x:c r="E81" s="166" t="str">
+        <x:v>製品バージョンとライフサイクルマスタの照合結果</x:v>
+      </x:c>
+      <x:c r="F81" s="166" t="str">
+        <x:v>顧客ライフサイクルマスタ</x:v>
+      </x:c>
+      <x:c r="G81" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H81" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I81" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J81" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できるが、AV ヘルス、指定製品、ライフサイクル判定は標準ターゲット項目ではない。</x:v>
+      </x:c>
+      <x:c r="K81" s="166" t="str">
+        <x:v>公式情報に基づく推定 / 顧客ルール</x:v>
+      </x:c>
+      <x:c r="L81" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="63" customHeight="1">
+      <x:c r="A82" s="165" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B82" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C82" s="166" t="str">
+        <x:v>ウイルス対策製品が指定製品ではない</x:v>
+      </x:c>
+      <x:c r="D82" s="166" t="str">
+        <x:v>未導入 / 指定外 / サポート終了判定</x:v>
+      </x:c>
+      <x:c r="E82" s="166" t="str">
+        <x:v>ソフトウェアインベントリ + AV ヘルス状態 + 顧客ルール</x:v>
+      </x:c>
+      <x:c r="F82" s="166" t="str">
+        <x:v>算出項目</x:v>
+      </x:c>
+      <x:c r="G82" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H82" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I82" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J82" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できるが、AV ヘルス、指定製品、ライフサイクル判定は標準ターゲット項目ではない。</x:v>
+      </x:c>
+      <x:c r="K82" s="166" t="str">
+        <x:v>公式情報に基づく推定 / 顧客ルール</x:v>
+      </x:c>
+      <x:c r="L82" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="63" customHeight="1">
+      <x:c r="A83" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B83" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C83" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D83" s="98" t="str">
+        <x:v>AV 製品名</x:v>
+      </x:c>
+      <x:c r="E83" s="98" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F83" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G83" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H83" s="98" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I83" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J83" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K83" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L83" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="63" customHeight="1">
+      <x:c r="A84" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B84" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C84" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D84" s="98" t="str">
+        <x:v>AV 製品バージョン</x:v>
+      </x:c>
+      <x:c r="E84" s="98" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F84" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G84" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H84" s="98" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I84" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J84" s="98" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K84" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L84" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="63" customHeight="1">
+      <x:c r="A85" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B85" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C85" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D85" s="98" t="str">
+        <x:v>AV 製品 Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E85" s="98" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F85" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G85" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H85" s="98" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I85" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J85" s="98" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K85" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L85" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="63" customHeight="1">
+      <x:c r="A86" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B86" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C86" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D86" s="98" t="str">
+        <x:v>AV 製品インストール日</x:v>
+      </x:c>
+      <x:c r="E86" s="98" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F86" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G86" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H86" s="98" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I86" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J86" s="98" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K86" s="98" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L86" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="63" customHeight="1">
+      <x:c r="A87" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B87" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C87" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D87" s="98" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E87" s="98" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F87" s="98" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G87" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H87" s="98" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I87" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J87" s="98" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K87" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L87" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="63" customHeight="1">
+      <x:c r="A88" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B88" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C88" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D88" s="98" t="str">
+        <x:v>ライフサイクル段階</x:v>
+      </x:c>
+      <x:c r="E88" s="98" t="str">
+        <x:v>顧客 AV ライフサイクルマスタの Stage</x:v>
+      </x:c>
+      <x:c r="F88" s="98" t="str">
+        <x:v>顧客ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G88" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H88" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I88" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J88" s="98" t="str">
+        <x:v>製品インストール情報は標準格納できる。移行期限と段階は顧客が管理する業務ルールである。</x:v>
+      </x:c>
+      <x:c r="K88" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L88" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="63" customHeight="1">
+      <x:c r="A89" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B89" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C89" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D89" s="98" t="str">
+        <x:v>移行期限日</x:v>
+      </x:c>
+      <x:c r="E89" s="98" t="str">
+        <x:v>顧客 AV ライフサイクルマスタの Due Date</x:v>
+      </x:c>
+      <x:c r="F89" s="98" t="str">
+        <x:v>顧客ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G89" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H89" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I89" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J89" s="98" t="str">
+        <x:v>製品インストール情報は標準格納できる。移行期限と段階は顧客が管理する業務ルールである。</x:v>
+      </x:c>
+      <x:c r="K89" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L89" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="63" customHeight="1">
+      <x:c r="A90" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B90" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C90" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D90" s="98" t="str">
+        <x:v>残日数</x:v>
+      </x:c>
+      <x:c r="E90" s="98" t="str">
+        <x:v>Due Date - 判定日</x:v>
+      </x:c>
+      <x:c r="F90" s="98" t="str">
+        <x:v>顧客ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G90" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H90" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I90" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J90" s="98" t="str">
+        <x:v>製品インストール情報は標準格納できる。移行期限と段階は顧客が管理する業務ルールである。</x:v>
+      </x:c>
+      <x:c r="K90" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L90" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="63" customHeight="1">
+      <x:c r="A91" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B91" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C91" s="98" t="str">
+        <x:v>AV 製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D91" s="98" t="str">
+        <x:v>移行段階判定結果</x:v>
+      </x:c>
+      <x:c r="E91" s="98" t="str">
+        <x:v>製品名 / バージョンとライフサイクルマスタの照合結果</x:v>
+      </x:c>
+      <x:c r="F91" s="98" t="str">
+        <x:v>顧客ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G91" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H91" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I91" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J91" s="98" t="str">
+        <x:v>製品インストール情報は標準格納できる。移行期限と段階は顧客が管理する業務ルールである。</x:v>
+      </x:c>
+      <x:c r="K91" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L91" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="63" customHeight="1">
+      <x:c r="A92" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B92" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C92" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D92" s="166" t="str">
+        <x:v>AV 製品名</x:v>
+      </x:c>
+      <x:c r="E92" s="166" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F92" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G92" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H92" s="166" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I92" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J92" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K92" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L92" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="63" customHeight="1">
+      <x:c r="A93" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B93" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C93" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D93" s="166" t="str">
+        <x:v>AV 製品バージョン</x:v>
+      </x:c>
+      <x:c r="E93" s="166" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F93" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G93" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H93" s="166" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I93" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J93" s="166" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K93" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L93" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="63" customHeight="1">
+      <x:c r="A94" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B94" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C94" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D94" s="166" t="str">
+        <x:v>AV 製品 Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E94" s="166" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F94" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G94" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H94" s="166" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I94" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J94" s="166" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K94" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L94" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="63" customHeight="1">
+      <x:c r="A95" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B95" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C95" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D95" s="166" t="str">
+        <x:v>AV 製品インストール日</x:v>
+      </x:c>
+      <x:c r="E95" s="166" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F95" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G95" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H95" s="166" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I95" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J95" s="166" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K95" s="166" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L95" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="63" customHeight="1">
+      <x:c r="A96" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B96" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C96" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D96" s="166" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E96" s="166" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F96" s="166" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G96" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H96" s="166" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I96" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J96" s="166" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K96" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L96" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="63" customHeight="1">
+      <x:c r="A97" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B97" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C97" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D97" s="166" t="str">
+        <x:v>ライフサイクル段階</x:v>
+      </x:c>
+      <x:c r="E97" s="166" t="str">
+        <x:v>顧客 AV ライフサイクルマスタの Stage</x:v>
+      </x:c>
+      <x:c r="F97" s="166" t="str">
+        <x:v>顧客ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G97" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H97" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I97" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J97" s="166" t="str">
+        <x:v>製品インストール情報は標準格納できる。移行期限と段階は顧客が管理する業務ルールである。</x:v>
+      </x:c>
+      <x:c r="K97" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L97" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="63" customHeight="1">
+      <x:c r="A98" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B98" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C98" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D98" s="166" t="str">
+        <x:v>移行期限日</x:v>
+      </x:c>
+      <x:c r="E98" s="166" t="str">
+        <x:v>顧客 AV ライフサイクルマスタの Due Date</x:v>
+      </x:c>
+      <x:c r="F98" s="166" t="str">
+        <x:v>顧客ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G98" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H98" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I98" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J98" s="166" t="str">
+        <x:v>製品インストール情報は標準格納できる。移行期限と段階は顧客が管理する業務ルールである。</x:v>
+      </x:c>
+      <x:c r="K98" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L98" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="63" customHeight="1">
+      <x:c r="A99" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B99" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C99" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D99" s="166" t="str">
+        <x:v>残日数</x:v>
+      </x:c>
+      <x:c r="E99" s="166" t="str">
+        <x:v>Due Date - 判定日</x:v>
+      </x:c>
+      <x:c r="F99" s="166" t="str">
+        <x:v>顧客ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G99" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H99" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I99" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J99" s="166" t="str">
+        <x:v>製品インストール情報は標準格納できる。移行期限と段階は顧客が管理する業務ルールである。</x:v>
+      </x:c>
+      <x:c r="K99" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L99" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="63" customHeight="1">
+      <x:c r="A100" s="165" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B100" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C100" s="166" t="str">
+        <x:v>AV 製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D100" s="166" t="str">
+        <x:v>移行段階判定結果</x:v>
+      </x:c>
+      <x:c r="E100" s="166" t="str">
+        <x:v>製品名 / バージョンとライフサイクルマスタの照合結果</x:v>
+      </x:c>
+      <x:c r="F100" s="166" t="str">
+        <x:v>顧客ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G100" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H100" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I100" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J100" s="166" t="str">
+        <x:v>製品インストール情報は標準格納できる。移行期限と段階は顧客が管理する業務ルールである。</x:v>
+      </x:c>
+      <x:c r="K100" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L100" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="63" customHeight="1">
+      <x:c r="A101" s="99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B101" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C101" s="98" t="str">
+        <x:v>AutoProtect 未設定</x:v>
+      </x:c>
+      <x:c r="D101" s="98" t="str">
+        <x:v>AV 製品名</x:v>
+      </x:c>
+      <x:c r="E101" s="98" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F101" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G101" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H101" s="98" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I101" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J101" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K101" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L101" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="63" customHeight="1">
+      <x:c r="A102" s="99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B102" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C102" s="98" t="str">
+        <x:v>AutoProtect 未設定</x:v>
+      </x:c>
+      <x:c r="D102" s="98" t="str">
+        <x:v>AV 製品バージョン</x:v>
+      </x:c>
+      <x:c r="E102" s="98" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F102" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G102" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H102" s="98" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I102" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J102" s="98" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K102" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L102" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="63" customHeight="1">
+      <x:c r="A103" s="99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B103" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C103" s="98" t="str">
+        <x:v>AutoProtect 未設定</x:v>
+      </x:c>
+      <x:c r="D103" s="98" t="str">
+        <x:v>AV 製品 Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E103" s="98" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F103" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G103" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H103" s="98" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I103" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J103" s="98" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K103" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L103" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="63" customHeight="1">
+      <x:c r="A104" s="99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B104" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C104" s="98" t="str">
+        <x:v>AutoProtect 未設定</x:v>
+      </x:c>
+      <x:c r="D104" s="98" t="str">
+        <x:v>AV 製品インストール日</x:v>
+      </x:c>
+      <x:c r="E104" s="98" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F104" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G104" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H104" s="98" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I104" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J104" s="98" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K104" s="98" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L104" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="63" customHeight="1">
+      <x:c r="A105" s="99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B105" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C105" s="98" t="str">
+        <x:v>AutoProtect 未設定</x:v>
+      </x:c>
+      <x:c r="D105" s="98" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E105" s="98" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F105" s="98" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G105" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H105" s="98" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I105" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J105" s="98" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K105" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L105" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="63" customHeight="1">
+      <x:c r="A106" s="99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B106" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C106" s="98" t="str">
+        <x:v>AutoProtect 未設定</x:v>
+      </x:c>
+      <x:c r="D106" s="98" t="str">
+        <x:v>AutoProtect / リアルタイム保護の有効 / 無効</x:v>
+      </x:c>
+      <x:c r="E106" s="98" t="str">
+        <x:v>RealTimeProtectionEnabled / AutoProtectEnabled（製品依存）</x:v>
+      </x:c>
+      <x:c r="F106" s="98" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / 製品固有 WMI / Compliance Baseline</x:v>
+      </x:c>
+      <x:c r="G106" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H106" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I106" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J106" s="98" t="str">
+        <x:v>AutoProtect は製品依存のヘルス / ポリシー項目であり、標準 SG-SCCM CMDB ターゲット項目の対象外である。</x:v>
+      </x:c>
+      <x:c r="K106" s="98" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L106" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="63" customHeight="1">
+      <x:c r="A107" s="99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B107" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C107" s="98" t="str">
+        <x:v>AutoProtect 未設定</x:v>
+      </x:c>
+      <x:c r="D107" s="98" t="str">
+        <x:v>AV ポリシー適用状態</x:v>
+      </x:c>
+      <x:c r="E107" s="98" t="str">
+        <x:v>Policy State / Compliance Result（製品依存）</x:v>
+      </x:c>
+      <x:c r="F107" s="98" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / 製品固有 WMI / Compliance Baseline</x:v>
+      </x:c>
+      <x:c r="G107" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H107" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I107" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J107" s="98" t="str">
+        <x:v>AutoProtect は製品依存のヘルス / ポリシー項目であり、標準 SG-SCCM CMDB ターゲット項目の対象外である。</x:v>
+      </x:c>
+      <x:c r="K107" s="98" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L107" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="63" customHeight="1">
+      <x:c r="A108" s="99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B108" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C108" s="98" t="str">
+        <x:v>AutoProtect 未設定</x:v>
+      </x:c>
+      <x:c r="D108" s="98" t="str">
+        <x:v>AutoProtect 未設定判定</x:v>
+      </x:c>
+      <x:c r="E108" s="98" t="str">
+        <x:v>リアルタイム保護値 + 製品ポリシールール</x:v>
+      </x:c>
+      <x:c r="F108" s="98" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / 製品固有 WMI / Compliance Baseline</x:v>
+      </x:c>
+      <x:c r="G108" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H108" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I108" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J108" s="98" t="str">
+        <x:v>AutoProtect は製品依存のヘルス / ポリシー項目であり、標準 SG-SCCM CMDB ターゲット項目の対象外である。</x:v>
+      </x:c>
+      <x:c r="K108" s="98" t="str">
+        <x:v>インスタンス依存</x:v>
+      </x:c>
+      <x:c r="L108" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="63" customHeight="1">
+      <x:c r="A109" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B109" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C109" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D109" s="166" t="str">
+        <x:v>AV 製品名</x:v>
+      </x:c>
+      <x:c r="E109" s="166" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F109" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G109" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H109" s="166" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I109" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J109" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K109" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L109" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="63" customHeight="1">
+      <x:c r="A110" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B110" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C110" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D110" s="166" t="str">
+        <x:v>AV 製品バージョン</x:v>
+      </x:c>
+      <x:c r="E110" s="166" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F110" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G110" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H110" s="166" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I110" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J110" s="166" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K110" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L110" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="63" customHeight="1">
+      <x:c r="A111" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B111" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C111" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D111" s="166" t="str">
+        <x:v>AV 製品 Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E111" s="166" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F111" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G111" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H111" s="166" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I111" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J111" s="166" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K111" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L111" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="63" customHeight="1">
+      <x:c r="A112" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B112" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C112" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D112" s="166" t="str">
+        <x:v>AV 製品インストール日</x:v>
+      </x:c>
+      <x:c r="E112" s="166" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F112" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G112" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H112" s="166" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I112" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J112" s="166" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K112" s="166" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L112" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="63" customHeight="1">
+      <x:c r="A113" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B113" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C113" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D113" s="166" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E113" s="166" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F113" s="166" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G113" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H113" s="166" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I113" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J113" s="166" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K113" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L113" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="63" customHeight="1">
+      <x:c r="A114" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B114" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C114" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D114" s="166" t="str">
+        <x:v>定義ファイル / セキュリティインテリジェンスバージョン</x:v>
+      </x:c>
+      <x:c r="E114" s="166" t="str">
+        <x:v>DefinitionVersion / SignatureVersion（候補）</x:v>
+      </x:c>
+      <x:c r="F114" s="166" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / v_EndpointProtectionStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G114" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H114" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I114" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J114" s="166" t="str">
+        <x:v>MECM Endpoint Protection はヘルス情報を提供できるが、標準 SG-SCCM CMDB ターゲット項目は定義ファイルとヘルス状態を対象としていない。</x:v>
+      </x:c>
+      <x:c r="K114" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L114" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="63" customHeight="1">
+      <x:c r="A115" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B115" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C115" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D115" s="166" t="str">
+        <x:v>定義ファイル最終更新日時</x:v>
+      </x:c>
+      <x:c r="E115" s="166" t="str">
+        <x:v>DefinitionLastUpdated / SignatureUpdated（候補）</x:v>
+      </x:c>
+      <x:c r="F115" s="166" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / v_EndpointProtectionStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G115" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H115" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I115" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J115" s="166" t="str">
+        <x:v>MECM Endpoint Protection はヘルス情報を提供できるが、標準 SG-SCCM CMDB ターゲット項目は定義ファイルとヘルス状態を対象としていない。</x:v>
+      </x:c>
+      <x:c r="K115" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L115" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="63" customHeight="1">
+      <x:c r="A116" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B116" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C116" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D116" s="166" t="str">
+        <x:v>Antimalware Engine バージョン</x:v>
+      </x:c>
+      <x:c r="E116" s="166" t="str">
+        <x:v>EngineVersion（候補）</x:v>
+      </x:c>
+      <x:c r="F116" s="166" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / v_EndpointProtectionStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G116" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H116" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I116" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J116" s="166" t="str">
+        <x:v>MECM Endpoint Protection はヘルス情報を提供できるが、標準 SG-SCCM CMDB ターゲット項目は定義ファイルとヘルス状態を対象としていない。</x:v>
+      </x:c>
+      <x:c r="K116" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L116" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="63" customHeight="1">
+      <x:c r="A117" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B117" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C117" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D117" s="166" t="str">
+        <x:v>AV の有効 / 無効</x:v>
+      </x:c>
+      <x:c r="E117" s="166" t="str">
+        <x:v>AntivirusEnabled / AntimalwareEnabled（候補）</x:v>
+      </x:c>
+      <x:c r="F117" s="166" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / v_EndpointProtectionStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G117" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H117" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I117" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J117" s="166" t="str">
+        <x:v>MECM Endpoint Protection はヘルス情報を提供できるが、標準 SG-SCCM CMDB ターゲット項目は定義ファイルとヘルス状態を対象としていない。</x:v>
+      </x:c>
+      <x:c r="K117" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L117" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="63" customHeight="1">
+      <x:c r="A118" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B118" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C118" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D118" s="166" t="str">
+        <x:v>定義ファイル更新後の経過日数</x:v>
+      </x:c>
+      <x:c r="E118" s="166" t="str">
+        <x:v>判定日 - 定義ファイル最終更新日時</x:v>
+      </x:c>
+      <x:c r="F118" s="166" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / v_EndpointProtectionStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G118" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H118" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I118" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J118" s="166" t="str">
+        <x:v>MECM Endpoint Protection はヘルス情報を提供できるが、標準 SG-SCCM CMDB ターゲット項目は定義ファイルとヘルス状態を対象としていない。</x:v>
+      </x:c>
+      <x:c r="K118" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L118" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="63" customHeight="1">
+      <x:c r="A119" s="165" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B119" s="166" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C119" s="166" t="str">
+        <x:v>AV 定義ファイルが最新ではない</x:v>
+      </x:c>
+      <x:c r="D119" s="166" t="str">
+        <x:v>1 週間以上未更新の判定</x:v>
+      </x:c>
+      <x:c r="E119" s="166" t="str">
+        <x:v>経過日数 &gt;= 顧客しきい値</x:v>
+      </x:c>
+      <x:c r="F119" s="166" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / v_EndpointProtectionStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G119" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H119" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I119" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J119" s="166" t="str">
+        <x:v>MECM Endpoint Protection はヘルス情報を提供できるが、標準 SG-SCCM CMDB ターゲット項目は定義ファイルとヘルス状態を対象としていない。</x:v>
+      </x:c>
+      <x:c r="K119" s="166" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L119" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="63" customHeight="1">
+      <x:c r="A120" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B120" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C120" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D120" s="98" t="str">
+        <x:v>AV 製品名</x:v>
+      </x:c>
+      <x:c r="E120" s="98" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F120" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G120" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H120" s="98" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I120" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J120" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K120" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L120" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="63" customHeight="1">
+      <x:c r="A121" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B121" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C121" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D121" s="98" t="str">
+        <x:v>AV 製品バージョン</x:v>
+      </x:c>
+      <x:c r="E121" s="98" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F121" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G121" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H121" s="98" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I121" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J121" s="98" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K121" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L121" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="63" customHeight="1">
+      <x:c r="A122" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B122" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C122" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D122" s="98" t="str">
+        <x:v>AV 製品 Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E122" s="98" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F122" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G122" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H122" s="98" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I122" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J122" s="98" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K122" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L122" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="63" customHeight="1">
+      <x:c r="A123" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B123" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C123" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D123" s="98" t="str">
+        <x:v>AV 製品インストール日</x:v>
+      </x:c>
+      <x:c r="E123" s="98" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F123" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G123" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H123" s="98" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I123" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J123" s="98" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K123" s="98" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L123" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="63" customHeight="1">
+      <x:c r="A124" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B124" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C124" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D124" s="98" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E124" s="98" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F124" s="98" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G124" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H124" s="98" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I124" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J124" s="98" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K124" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L124" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="63" customHeight="1">
+      <x:c r="A125" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B125" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C125" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D125" s="98" t="str">
+        <x:v>最終スキャン日時</x:v>
+      </x:c>
+      <x:c r="E125" s="98" t="str">
+        <x:v>LastScanTime / LastFullScanTime / LastQuickScanTime（候補）</x:v>
+      </x:c>
+      <x:c r="F125" s="98" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G125" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H125" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I125" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J125" s="98" t="str">
+        <x:v>MECM はスキャンヘルス情報を提供できるが、標準 SG-SCCM ターゲット項目に AV スキャン履歴はない。</x:v>
+      </x:c>
+      <x:c r="K125" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L125" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="63" customHeight="1">
+      <x:c r="A126" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B126" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C126" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D126" s="98" t="str">
+        <x:v>スキャン種別</x:v>
+      </x:c>
+      <x:c r="E126" s="98" t="str">
+        <x:v>Full / Quick / Scheduled（候補）</x:v>
+      </x:c>
+      <x:c r="F126" s="98" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G126" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H126" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I126" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J126" s="98" t="str">
+        <x:v>MECM はスキャンヘルス情報を提供できるが、標準 SG-SCCM ターゲット項目に AV スキャン履歴はない。</x:v>
+      </x:c>
+      <x:c r="K126" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L126" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="63" customHeight="1">
+      <x:c r="A127" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B127" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C127" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D127" s="98" t="str">
+        <x:v>スキャン結果 / ヘルス状態</x:v>
+      </x:c>
+      <x:c r="E127" s="98" t="str">
+        <x:v>Scan Result / Health State（候補）</x:v>
+      </x:c>
+      <x:c r="F127" s="98" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G127" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H127" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I127" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J127" s="98" t="str">
+        <x:v>MECM はスキャンヘルス情報を提供できるが、標準 SG-SCCM ターゲット項目に AV スキャン履歴はない。</x:v>
+      </x:c>
+      <x:c r="K127" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L127" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="63" customHeight="1">
+      <x:c r="A128" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B128" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C128" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D128" s="98" t="str">
+        <x:v>最終スキャンからの経過日数</x:v>
+      </x:c>
+      <x:c r="E128" s="98" t="str">
+        <x:v>判定日 - LastScanTime</x:v>
+      </x:c>
+      <x:c r="F128" s="98" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G128" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H128" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I128" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J128" s="98" t="str">
+        <x:v>MECM はスキャンヘルス情報を提供できるが、標準 SG-SCCM ターゲット項目に AV スキャン履歴はない。</x:v>
+      </x:c>
+      <x:c r="K128" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L128" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="63" customHeight="1">
+      <x:c r="A129" s="99" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B129" s="98" t="str">
+        <x:v>AV / Endpoint Protection</x:v>
+      </x:c>
+      <x:c r="C129" s="98" t="str">
+        <x:v>AV 定期スキャンが 1 週間以上未実施</x:v>
+      </x:c>
+      <x:c r="D129" s="98" t="str">
+        <x:v>1 週間以上未スキャンの判定</x:v>
+      </x:c>
+      <x:c r="E129" s="98" t="str">
+        <x:v>経過日数 &gt;= 顧客しきい値</x:v>
+      </x:c>
+      <x:c r="F129" s="98" t="str">
+        <x:v>v_GS_AntimalwareHealthStatus / 算出項目</x:v>
+      </x:c>
+      <x:c r="G129" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H129" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I129" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J129" s="98" t="str">
+        <x:v>MECM はスキャンヘルス情報を提供できるが、標準 SG-SCCM ターゲット項目に AV スキャン履歴はない。</x:v>
+      </x:c>
+      <x:c r="K129" s="98" t="str">
+        <x:v>Microsoft 公式 + ServiceNow ターゲット表照合</x:v>
+      </x:c>
+      <x:c r="L129" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/endpoint-protection-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="63" customHeight="1">
+      <x:c r="A130" s="165" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B130" s="166" t="str">
+        <x:v>ディスク暗号化</x:v>
+      </x:c>
+      <x:c r="C130" s="166" t="str">
+        <x:v>HDD 未暗号化</x:v>
+      </x:c>
+      <x:c r="D130" s="166" t="str">
+        <x:v>ディスク / ボリューム名</x:v>
+      </x:c>
+      <x:c r="E130" s="166" t="str">
+        <x:v>Name0 / DeviceID0 / DriveLetter0（候補）</x:v>
+      </x:c>
+      <x:c r="F130" s="166" t="str">
+        <x:v>v_GS_ENCRYPTABLE_VOLUME / v_GS_PROTECTED_VOLUME_INFO / v_GS_TPM / v_GS_DISK</x:v>
+      </x:c>
+      <x:c r="G130" s="166" t="str">
+        <x:v>cmdb_ci_disk</x:v>
+      </x:c>
+      <x:c r="H130" s="166" t="str">
+        <x:v>name / device_id</x:v>
+      </x:c>
+      <x:c r="I130" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J130" s="166" t="str">
+        <x:v>標準 SG-SCCM は Disk の識別情報を取り込める。暗号化 View のボリュームとの対応付けが必要である。</x:v>
+      </x:c>
+      <x:c r="K130" s="166" t="str">
+        <x:v>公式サポート・関連付け要確認</x:v>
+      </x:c>
+      <x:c r="L130" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="63" customHeight="1">
+      <x:c r="A131" s="165" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B131" s="166" t="str">
+        <x:v>ディスク暗号化</x:v>
+      </x:c>
+      <x:c r="C131" s="166" t="str">
+        <x:v>HDD 未暗号化</x:v>
+      </x:c>
+      <x:c r="D131" s="166" t="str">
+        <x:v>ディスク容量</x:v>
+      </x:c>
+      <x:c r="E131" s="166" t="str">
+        <x:v>Size0（候補）</x:v>
+      </x:c>
+      <x:c r="F131" s="166" t="str">
+        <x:v>v_GS_ENCRYPTABLE_VOLUME / v_GS_PROTECTED_VOLUME_INFO / v_GS_TPM / v_GS_DISK</x:v>
+      </x:c>
+      <x:c r="G131" s="166" t="str">
+        <x:v>cmdb_ci_disk</x:v>
+      </x:c>
+      <x:c r="H131" s="166" t="str">
+        <x:v>size_bytes / disk_space</x:v>
+      </x:c>
+      <x:c r="I131" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J131" s="166" t="str">
+        <x:v>標準ターゲット項目にディスク容量が明記されている。</x:v>
+      </x:c>
+      <x:c r="K131" s="166" t="str">
+        <x:v>公式サポート・関連付け要確認</x:v>
+      </x:c>
+      <x:c r="L131" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="63" customHeight="1">
+      <x:c r="A132" s="165" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B132" s="166" t="str">
+        <x:v>ディスク暗号化</x:v>
+      </x:c>
+      <x:c r="C132" s="166" t="str">
+        <x:v>HDD 未暗号化</x:v>
+      </x:c>
+      <x:c r="D132" s="166" t="str">
+        <x:v>ドライブ種類</x:v>
+      </x:c>
+      <x:c r="E132" s="166" t="str">
+        <x:v>DriveType0（候補）</x:v>
+      </x:c>
+      <x:c r="F132" s="166" t="str">
+        <x:v>v_GS_ENCRYPTABLE_VOLUME / v_GS_PROTECTED_VOLUME_INFO / v_GS_TPM / v_GS_DISK</x:v>
+      </x:c>
+      <x:c r="G132" s="166" t="str">
+        <x:v>cmdb_ci_disk</x:v>
+      </x:c>
+      <x:c r="H132" s="166" t="str">
+        <x:v>drive_type</x:v>
+      </x:c>
+      <x:c r="I132" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J132" s="166" t="str">
+        <x:v>標準ターゲット項目に drive_type が明記されている。</x:v>
+      </x:c>
+      <x:c r="K132" s="166" t="str">
+        <x:v>公式サポート・関連付け要確認</x:v>
+      </x:c>
+      <x:c r="L132" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="63" customHeight="1">
+      <x:c r="A133" s="165" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B133" s="166" t="str">
+        <x:v>ディスク暗号化</x:v>
+      </x:c>
+      <x:c r="C133" s="166" t="str">
+        <x:v>HDD 未暗号化</x:v>
+      </x:c>
+      <x:c r="D133" s="166" t="str">
+        <x:v>BitLocker 保護状態</x:v>
+      </x:c>
+      <x:c r="E133" s="166" t="str">
+        <x:v>ProtectionStatus0（候補）</x:v>
+      </x:c>
+      <x:c r="F133" s="166" t="str">
+        <x:v>v_GS_ENCRYPTABLE_VOLUME / v_GS_PROTECTED_VOLUME_INFO / v_GS_TPM / v_GS_DISK</x:v>
+      </x:c>
+      <x:c r="G133" s="166" t="str">
+        <x:v>標準ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H133" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I133" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J133" s="166" t="str">
+        <x:v>標準 cmdb_ci_disk ターゲット項目に暗号化保護状態はない。</x:v>
+      </x:c>
+      <x:c r="K133" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L133" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="63" customHeight="1">
+      <x:c r="A134" s="165" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B134" s="166" t="str">
+        <x:v>ディスク暗号化</x:v>
+      </x:c>
+      <x:c r="C134" s="166" t="str">
+        <x:v>HDD 未暗号化</x:v>
+      </x:c>
+      <x:c r="D134" s="166" t="str">
+        <x:v>暗号化変換状態</x:v>
+      </x:c>
+      <x:c r="E134" s="166" t="str">
+        <x:v>ConversionStatus0（候補）</x:v>
+      </x:c>
+      <x:c r="F134" s="166" t="str">
+        <x:v>v_GS_ENCRYPTABLE_VOLUME / v_GS_PROTECTED_VOLUME_INFO / v_GS_TPM / v_GS_DISK</x:v>
+      </x:c>
+      <x:c r="G134" s="166" t="str">
+        <x:v>標準ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H134" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I134" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J134" s="166" t="str">
+        <x:v>標準 cmdb_ci_disk ターゲット項目に変換状態はない。</x:v>
+      </x:c>
+      <x:c r="K134" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L134" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="63" customHeight="1">
+      <x:c r="A135" s="165" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B135" s="166" t="str">
+        <x:v>ディスク暗号化</x:v>
+      </x:c>
+      <x:c r="C135" s="166" t="str">
+        <x:v>HDD 未暗号化</x:v>
+      </x:c>
+      <x:c r="D135" s="166" t="str">
+        <x:v>暗号化方式</x:v>
+      </x:c>
+      <x:c r="E135" s="166" t="str">
+        <x:v>EncryptionMethod0（候補）</x:v>
+      </x:c>
+      <x:c r="F135" s="166" t="str">
+        <x:v>v_GS_ENCRYPTABLE_VOLUME / v_GS_PROTECTED_VOLUME_INFO / v_GS_TPM / v_GS_DISK</x:v>
+      </x:c>
+      <x:c r="G135" s="166" t="str">
+        <x:v>標準ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H135" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I135" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J135" s="166" t="str">
+        <x:v>標準 cmdb_ci_disk ターゲット項目に暗号化方式はない。</x:v>
+      </x:c>
+      <x:c r="K135" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L135" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="63" customHeight="1">
+      <x:c r="A136" s="165" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B136" s="166" t="str">
+        <x:v>ディスク暗号化</x:v>
+      </x:c>
+      <x:c r="C136" s="166" t="str">
+        <x:v>HDD 未暗号化</x:v>
+      </x:c>
+      <x:c r="D136" s="166" t="str">
+        <x:v>TPM 状態 / バージョン</x:v>
+      </x:c>
+      <x:c r="E136" s="166" t="str">
+        <x:v>TPM 属性（候補）</x:v>
+      </x:c>
+      <x:c r="F136" s="166" t="str">
+        <x:v>v_GS_ENCRYPTABLE_VOLUME / v_GS_PROTECTED_VOLUME_INFO / v_GS_TPM / v_GS_DISK</x:v>
+      </x:c>
+      <x:c r="G136" s="166" t="str">
+        <x:v>標準ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H136" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I136" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J136" s="166" t="str">
+        <x:v>MECM は TPM を収集できるが、SG-SCCM 標準ターゲットクラス一覧に TPM のターゲットテーブル / 項目はない。</x:v>
+      </x:c>
+      <x:c r="K136" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L136" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="63" customHeight="1">
+      <x:c r="A137" s="165" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B137" s="166" t="str">
+        <x:v>ディスク暗号化</x:v>
+      </x:c>
+      <x:c r="C137" s="166" t="str">
+        <x:v>HDD 未暗号化</x:v>
+      </x:c>
+      <x:c r="D137" s="166" t="str">
+        <x:v>HDD 未暗号化判定</x:v>
+      </x:c>
+      <x:c r="E137" s="166" t="str">
+        <x:v>ProtectionStatus + 顧客判定ルール</x:v>
+      </x:c>
+      <x:c r="F137" s="166" t="str">
+        <x:v>v_GS_ENCRYPTABLE_VOLUME / v_GS_PROTECTED_VOLUME_INFO / v_GS_TPM / v_GS_DISK</x:v>
+      </x:c>
+      <x:c r="G137" s="166" t="str">
+        <x:v>標準ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H137" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I137" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J137" s="166" t="str">
+        <x:v>コンプライアンス判定結果であり、カスタムセキュリティ発見テーブルへ格納する。</x:v>
+      </x:c>
+      <x:c r="K137" s="166" t="str">
+        <x:v>公式情報に基づく推定</x:v>
+      </x:c>
+      <x:c r="L137" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="63" customHeight="1">
+      <x:c r="A138" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B138" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C138" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D138" s="98" t="str">
+        <x:v>ソフトウェア名</x:v>
+      </x:c>
+      <x:c r="E138" s="98" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F138" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G138" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H138" s="98" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I138" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J138" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K138" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L138" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="63" customHeight="1">
+      <x:c r="A139" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B139" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C139" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D139" s="98" t="str">
+        <x:v>ソフトウェアバージョン</x:v>
+      </x:c>
+      <x:c r="E139" s="98" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F139" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G139" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H139" s="98" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I139" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J139" s="98" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K139" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L139" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="63" customHeight="1">
+      <x:c r="A140" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B140" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C140" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D140" s="98" t="str">
+        <x:v>ソフトウェア Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E140" s="98" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F140" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G140" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H140" s="98" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I140" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J140" s="98" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K140" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L140" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="63" customHeight="1">
+      <x:c r="A141" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B141" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C141" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D141" s="98" t="str">
+        <x:v>ソフトウェアインストール日</x:v>
+      </x:c>
+      <x:c r="E141" s="98" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F141" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G141" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H141" s="98" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I141" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J141" s="98" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K141" s="98" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L141" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="63" customHeight="1">
+      <x:c r="A142" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B142" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C142" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D142" s="98" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E142" s="98" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F142" s="98" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G142" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H142" s="98" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I142" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J142" s="98" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K142" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L142" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="63" customHeight="1">
+      <x:c r="A143" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B143" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C143" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D143" s="98" t="str">
+        <x:v>ソフトウェア分類 / Category</x:v>
+      </x:c>
+      <x:c r="E143" s="98" t="str">
+        <x:v>CategoryID / Category Name（Asset Intelligence 候補）</x:v>
+      </x:c>
+      <x:c r="F143" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G143" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H143" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I143" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J143" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K143" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L143" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="63" customHeight="1">
+      <x:c r="A144" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B144" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C144" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D144" s="98" t="str">
+        <x:v>禁止ソフトウェアリストとの照合結果</x:v>
+      </x:c>
+      <x:c r="E144" s="98" t="str">
+        <x:v>ソフトウェア名 / バージョンと顧客禁止リストの照合結果</x:v>
+      </x:c>
+      <x:c r="F144" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G144" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H144" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I144" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J144" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K144" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L144" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="63" customHeight="1">
+      <x:c r="A145" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B145" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C145" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D145" s="98" t="str">
+        <x:v>リスクレベル</x:v>
+      </x:c>
+      <x:c r="E145" s="98" t="str">
+        <x:v>顧客ルールにより High と固定 / 算出</x:v>
+      </x:c>
+      <x:c r="F145" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G145" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H145" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I145" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J145" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K145" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L145" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="63" customHeight="1">
+      <x:c r="A146" s="99" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B146" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C146" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（高）</x:v>
+      </x:c>
+      <x:c r="D146" s="98" t="str">
+        <x:v>最終指摘判定</x:v>
+      </x:c>
+      <x:c r="E146" s="98" t="str">
+        <x:v>インストール済みソフトウェア + 禁止リスト + リスクレベル</x:v>
+      </x:c>
+      <x:c r="F146" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G146" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H146" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I146" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J146" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K146" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L146" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="63" customHeight="1">
+      <x:c r="A147" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B147" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C147" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D147" s="166" t="str">
+        <x:v>ソフトウェア名</x:v>
+      </x:c>
+      <x:c r="E147" s="166" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F147" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G147" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H147" s="166" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I147" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J147" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K147" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L147" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="63" customHeight="1">
+      <x:c r="A148" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B148" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C148" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D148" s="166" t="str">
+        <x:v>ソフトウェアバージョン</x:v>
+      </x:c>
+      <x:c r="E148" s="166" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F148" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G148" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H148" s="166" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I148" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J148" s="166" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K148" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L148" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="63" customHeight="1">
+      <x:c r="A149" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B149" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C149" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D149" s="166" t="str">
+        <x:v>ソフトウェア Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E149" s="166" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F149" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G149" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H149" s="166" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I149" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J149" s="166" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K149" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L149" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="63" customHeight="1">
+      <x:c r="A150" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B150" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C150" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D150" s="166" t="str">
+        <x:v>ソフトウェアインストール日</x:v>
+      </x:c>
+      <x:c r="E150" s="166" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F150" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G150" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H150" s="166" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I150" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J150" s="166" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K150" s="166" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L150" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="63" customHeight="1">
+      <x:c r="A151" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B151" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C151" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D151" s="166" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E151" s="166" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F151" s="166" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G151" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H151" s="166" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I151" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J151" s="166" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K151" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L151" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="63" customHeight="1">
+      <x:c r="A152" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B152" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C152" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D152" s="166" t="str">
+        <x:v>ソフトウェア分類 / Category</x:v>
+      </x:c>
+      <x:c r="E152" s="166" t="str">
+        <x:v>CategoryID / Category Name（Asset Intelligence 候補）</x:v>
+      </x:c>
+      <x:c r="F152" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G152" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H152" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I152" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J152" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K152" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L152" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="63" customHeight="1">
+      <x:c r="A153" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B153" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C153" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D153" s="166" t="str">
+        <x:v>禁止ソフトウェアリストとの照合結果</x:v>
+      </x:c>
+      <x:c r="E153" s="166" t="str">
+        <x:v>ソフトウェア名 / バージョンと顧客禁止リストの照合結果</x:v>
+      </x:c>
+      <x:c r="F153" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G153" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H153" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I153" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J153" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K153" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L153" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="63" customHeight="1">
+      <x:c r="A154" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B154" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C154" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D154" s="166" t="str">
+        <x:v>リスクレベル</x:v>
+      </x:c>
+      <x:c r="E154" s="166" t="str">
+        <x:v>顧客ルールにより Medium と固定 / 算出</x:v>
+      </x:c>
+      <x:c r="F154" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G154" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H154" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I154" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J154" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K154" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L154" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="63" customHeight="1">
+      <x:c r="A155" s="165" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B155" s="166" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C155" s="166" t="str">
+        <x:v>不適切ソフトウェア導入済み（中）</x:v>
+      </x:c>
+      <x:c r="D155" s="166" t="str">
+        <x:v>最終指摘判定</x:v>
+      </x:c>
+      <x:c r="E155" s="166" t="str">
+        <x:v>インストール済みソフトウェア + 禁止リスト + リスクレベル</x:v>
+      </x:c>
+      <x:c r="F155" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G155" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H155" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I155" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J155" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K155" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L155" s="166" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="63" customHeight="1">
+      <x:c r="A156" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B156" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C156" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D156" s="98" t="str">
+        <x:v>ソフトウェア名</x:v>
+      </x:c>
+      <x:c r="E156" s="98" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F156" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G156" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H156" s="98" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I156" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J156" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K156" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L156" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="63" customHeight="1">
+      <x:c r="A157" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B157" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C157" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D157" s="98" t="str">
+        <x:v>ソフトウェアバージョン</x:v>
+      </x:c>
+      <x:c r="E157" s="98" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F157" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G157" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H157" s="98" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I157" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J157" s="98" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K157" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L157" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="63" customHeight="1">
+      <x:c r="A158" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B158" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C158" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D158" s="98" t="str">
+        <x:v>ソフトウェア Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E158" s="98" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F158" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G158" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H158" s="98" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I158" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J158" s="98" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K158" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L158" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="63" customHeight="1">
+      <x:c r="A159" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B159" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C159" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D159" s="98" t="str">
+        <x:v>ソフトウェアインストール日</x:v>
+      </x:c>
+      <x:c r="E159" s="98" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F159" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G159" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H159" s="98" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I159" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J159" s="98" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K159" s="98" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L159" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="63" customHeight="1">
+      <x:c r="A160" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B160" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C160" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D160" s="98" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E160" s="98" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F160" s="98" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G160" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H160" s="98" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I160" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J160" s="98" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K160" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L160" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="63" customHeight="1">
+      <x:c r="A161" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B161" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C161" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D161" s="98" t="str">
+        <x:v>ソフトウェア分類 / Category</x:v>
+      </x:c>
+      <x:c r="E161" s="98" t="str">
+        <x:v>CategoryID / Category Name（Asset Intelligence 候補）</x:v>
+      </x:c>
+      <x:c r="F161" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G161" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H161" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I161" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J161" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K161" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L161" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="63" customHeight="1">
+      <x:c r="A162" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B162" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C162" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D162" s="98" t="str">
+        <x:v>禁止ソフトウェアリストとの照合結果</x:v>
+      </x:c>
+      <x:c r="E162" s="98" t="str">
+        <x:v>ソフトウェア名 / バージョンと顧客禁止リストの照合結果</x:v>
+      </x:c>
+      <x:c r="F162" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G162" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H162" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I162" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J162" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K162" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L162" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="63" customHeight="1">
+      <x:c r="A163" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B163" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C163" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D163" s="98" t="str">
+        <x:v>リスクレベル</x:v>
+      </x:c>
+      <x:c r="E163" s="98" t="str">
+        <x:v>顧客ルールにより Low と固定 / 算出</x:v>
+      </x:c>
+      <x:c r="F163" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G163" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H163" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I163" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J163" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K163" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L163" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="63" customHeight="1">
+      <x:c r="A164" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B164" s="98" t="str">
+        <x:v>不適切ソフトウェア</x:v>
+      </x:c>
+      <x:c r="C164" s="98" t="str">
+        <x:v>不適切ソフトウェア導入済み（低）</x:v>
+      </x:c>
+      <x:c r="D164" s="98" t="str">
+        <x:v>最終指摘判定</x:v>
+      </x:c>
+      <x:c r="E164" s="98" t="str">
+        <x:v>インストール済みソフトウェア + 禁止リスト + リスクレベル</x:v>
+      </x:c>
+      <x:c r="F164" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE_CATEGORIZED / 顧客禁止ソフトウェアマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G164" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H164" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I164" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J164" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報を取り込めるが、顧客定義の不適切分類、リスクレベル、最終判定に対応する標準 CMDB 項目はない。</x:v>
+      </x:c>
+      <x:c r="K164" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L164" s="98" t="str">
+        <x:v>https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager
+https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="63" customHeight="1">
+      <x:c r="A165" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B165" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C165" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D165" s="166" t="str">
+        <x:v>ソフトウェア名</x:v>
+      </x:c>
+      <x:c r="E165" s="166" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F165" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G165" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H165" s="166" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I165" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J165" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K165" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L165" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="63" customHeight="1">
+      <x:c r="A166" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B166" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C166" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D166" s="166" t="str">
+        <x:v>ソフトウェアバージョン</x:v>
+      </x:c>
+      <x:c r="E166" s="166" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F166" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G166" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H166" s="166" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I166" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J166" s="166" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K166" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L166" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="63" customHeight="1">
+      <x:c r="A167" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B167" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C167" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D167" s="166" t="str">
+        <x:v>ソフトウェア Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E167" s="166" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F167" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G167" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H167" s="166" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I167" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J167" s="166" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K167" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L167" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="63" customHeight="1">
+      <x:c r="A168" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B168" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C168" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D168" s="166" t="str">
+        <x:v>ソフトウェアインストール日</x:v>
+      </x:c>
+      <x:c r="E168" s="166" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F168" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G168" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H168" s="166" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I168" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J168" s="166" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K168" s="166" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L168" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="63" customHeight="1">
+      <x:c r="A169" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B169" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C169" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D169" s="166" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E169" s="166" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F169" s="166" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G169" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H169" s="166" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I169" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J169" s="166" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K169" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L169" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="63" customHeight="1">
+      <x:c r="A170" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B170" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C170" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D170" s="166" t="str">
+        <x:v>製品ライフサイクル段階</x:v>
+      </x:c>
+      <x:c r="E170" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタの Stage=EOL</x:v>
+      </x:c>
+      <x:c r="F170" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G170" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H170" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I170" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J170" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K170" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L170" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="63" customHeight="1">
+      <x:c r="A171" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B171" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C171" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D171" s="166" t="str">
+        <x:v>サポート終了日 / 移行期限日</x:v>
+      </x:c>
+      <x:c r="E171" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタの Date</x:v>
+      </x:c>
+      <x:c r="F171" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G171" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H171" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I171" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J171" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K171" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L171" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="63" customHeight="1">
+      <x:c r="A172" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B172" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C172" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D172" s="166" t="str">
+        <x:v>期限までの残日数</x:v>
+      </x:c>
+      <x:c r="E172" s="166" t="str">
+        <x:v>期限日 - 判定日</x:v>
+      </x:c>
+      <x:c r="F172" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G172" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H172" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I172" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J172" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K172" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L172" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="63" customHeight="1">
+      <x:c r="A173" s="165" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B173" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C173" s="166" t="str">
+        <x:v>サポート終了製品導入済み</x:v>
+      </x:c>
+      <x:c r="D173" s="166" t="str">
+        <x:v>ライフサイクル指摘判定</x:v>
+      </x:c>
+      <x:c r="E173" s="166" t="str">
+        <x:v>ソフトウェア名 / バージョンとライフサイクルマスタの照合結果</x:v>
+      </x:c>
+      <x:c r="F173" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G173" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H173" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I173" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J173" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K173" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L173" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="63" customHeight="1">
+      <x:c r="A174" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B174" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C174" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D174" s="98" t="str">
+        <x:v>ソフトウェア名</x:v>
+      </x:c>
+      <x:c r="E174" s="98" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F174" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G174" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H174" s="98" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I174" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J174" s="98" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K174" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L174" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="63" customHeight="1">
+      <x:c r="A175" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B175" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C175" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D175" s="98" t="str">
+        <x:v>ソフトウェアバージョン</x:v>
+      </x:c>
+      <x:c r="E175" s="98" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F175" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G175" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H175" s="98" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I175" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J175" s="98" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K175" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L175" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="63" customHeight="1">
+      <x:c r="A176" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B176" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C176" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D176" s="98" t="str">
+        <x:v>ソフトウェア Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E176" s="98" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F176" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G176" s="98" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H176" s="98" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I176" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J176" s="98" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K176" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L176" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="63" customHeight="1">
+      <x:c r="A177" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B177" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C177" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D177" s="98" t="str">
+        <x:v>ソフトウェアインストール日</x:v>
+      </x:c>
+      <x:c r="E177" s="98" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F177" s="98" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G177" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H177" s="98" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I177" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J177" s="98" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K177" s="98" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L177" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="63" customHeight="1">
+      <x:c r="A178" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B178" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C178" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D178" s="98" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E178" s="98" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F178" s="98" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G178" s="98" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H178" s="98" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I178" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J178" s="98" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K178" s="98" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L178" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="63" customHeight="1">
+      <x:c r="A179" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B179" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C179" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D179" s="98" t="str">
+        <x:v>製品ライフサイクル段階</x:v>
+      </x:c>
+      <x:c r="E179" s="98" t="str">
+        <x:v>顧客製品ライフサイクルマスタの Stage=Warning</x:v>
+      </x:c>
+      <x:c r="F179" s="98" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G179" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H179" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I179" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J179" s="98" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K179" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L179" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="63" customHeight="1">
+      <x:c r="A180" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B180" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C180" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D180" s="98" t="str">
+        <x:v>サポート終了日 / 移行期限日</x:v>
+      </x:c>
+      <x:c r="E180" s="98" t="str">
+        <x:v>顧客製品ライフサイクルマスタの Date</x:v>
+      </x:c>
+      <x:c r="F180" s="98" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G180" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H180" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I180" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J180" s="98" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K180" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L180" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="63" customHeight="1">
+      <x:c r="A181" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B181" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C181" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D181" s="98" t="str">
+        <x:v>期限までの残日数</x:v>
+      </x:c>
+      <x:c r="E181" s="98" t="str">
+        <x:v>期限日 - 判定日</x:v>
+      </x:c>
+      <x:c r="F181" s="98" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G181" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H181" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I181" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J181" s="98" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K181" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L181" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="63" customHeight="1">
+      <x:c r="A182" s="99" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B182" s="98" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C182" s="98" t="str">
+        <x:v>製品移行期限終了 3 か月前</x:v>
+      </x:c>
+      <x:c r="D182" s="98" t="str">
+        <x:v>ライフサイクル指摘判定</x:v>
+      </x:c>
+      <x:c r="E182" s="98" t="str">
+        <x:v>ソフトウェア名 / バージョンとライフサイクルマスタの照合結果</x:v>
+      </x:c>
+      <x:c r="F182" s="98" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G182" s="98" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H182" s="98" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I182" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J182" s="98" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K182" s="98" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L182" s="98" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="63" customHeight="1">
+      <x:c r="A183" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B183" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C183" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D183" s="166" t="str">
+        <x:v>ソフトウェア名</x:v>
+      </x:c>
+      <x:c r="E183" s="166" t="str">
+        <x:v>ProductName0 / DisplayName0（候補）</x:v>
+      </x:c>
+      <x:c r="F183" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G183" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_software_instance / cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H183" s="166" t="str">
+        <x:v>display_name
+または name</x:v>
+      </x:c>
+      <x:c r="I183" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J183" s="166" t="str">
+        <x:v>標準 Connector はソフトウェアインストール情報をサポートする。SAM ありの場合は cmdb_sam_sw_install、SAM なしの場合は Software Instance / Software を使用する。</x:v>
+      </x:c>
+      <x:c r="K183" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L183" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="63" customHeight="1">
+      <x:c r="A184" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B184" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C184" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D184" s="166" t="str">
+        <x:v>ソフトウェアバージョン</x:v>
+      </x:c>
+      <x:c r="E184" s="166" t="str">
+        <x:v>ProductVersion0 / Version0（候補）</x:v>
+      </x:c>
+      <x:c r="F184" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G184" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H184" s="166" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="I184" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J184" s="166" t="str">
+        <x:v>標準ターゲット項目に version が明記されている。</x:v>
+      </x:c>
+      <x:c r="K184" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L184" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="63" customHeight="1">
+      <x:c r="A185" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B185" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C185" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D185" s="166" t="str">
+        <x:v>ソフトウェア Publisher / ベンダー</x:v>
+      </x:c>
+      <x:c r="E185" s="166" t="str">
+        <x:v>Publisher0（候補）</x:v>
+      </x:c>
+      <x:c r="F185" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G185" s="166" t="str">
+        <x:v>cmdb_sam_sw_install（SAM あり）
+cmdb_ci_spkg（SAM なし）</x:v>
+      </x:c>
+      <x:c r="H185" s="166" t="str">
+        <x:v>publisher
+または vendor / manufacturer</x:v>
+      </x:c>
+      <x:c r="I185" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J185" s="166" t="str">
+        <x:v>標準ターゲット項目に publisher が明記されている。SAM なしの場合は Software テーブルの vendor / manufacturer が候補となる。</x:v>
+      </x:c>
+      <x:c r="K185" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L185" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="63" customHeight="1">
+      <x:c r="A186" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B186" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C186" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D186" s="166" t="str">
+        <x:v>ソフトウェアインストール日</x:v>
+      </x:c>
+      <x:c r="E186" s="166" t="str">
+        <x:v>InstallDate0（候補）</x:v>
+      </x:c>
+      <x:c r="F186" s="166" t="str">
+        <x:v>v_GS_INSTALLED_SOFTWARE / v_GS_ADD_REMOVE_PROGRAMS</x:v>
+      </x:c>
+      <x:c r="G186" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H186" s="166" t="str">
+        <x:v>install_date</x:v>
+      </x:c>
+      <x:c r="I186" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J186" s="166" t="str">
+        <x:v>標準ターゲット項目に install_date が明記されている。ソース値の有無は MECM インベントリデータに依存する。</x:v>
+      </x:c>
+      <x:c r="K186" s="166" t="str">
+        <x:v>公式明記・ソース値は環境依存</x:v>
+      </x:c>
+      <x:c r="L186" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="63" customHeight="1">
+      <x:c r="A187" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B187" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C187" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D187" s="166" t="str">
+        <x:v>インストール先 CI</x:v>
+      </x:c>
+      <x:c r="E187" s="166" t="str">
+        <x:v>ResourceID（端末関連付け用）</x:v>
+      </x:c>
+      <x:c r="F187" s="166" t="str">
+        <x:v>MECM クライアント別インベントリ View</x:v>
+      </x:c>
+      <x:c r="G187" s="166" t="str">
+        <x:v>cmdb_sam_sw_install
+または cmdb_software_instance</x:v>
+      </x:c>
+      <x:c r="H187" s="166" t="str">
+        <x:v>installed_on</x:v>
+      </x:c>
+      <x:c r="I187" s="169" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="J187" s="166" t="str">
+        <x:v>標準項目 installed_on は Computer CI を参照する。ResourceID と CI の照合は Connector / IRE マッピングで処理される。</x:v>
+      </x:c>
+      <x:c r="K187" s="166" t="str">
+        <x:v>公式明記</x:v>
+      </x:c>
+      <x:c r="L187" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://www.servicenow.com/docs/r/servicenow-platform/service-graph-connectors/cmdb-integration-sccm.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="63" customHeight="1">
+      <x:c r="A188" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B188" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C188" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D188" s="166" t="str">
+        <x:v>製品ライフサイクル段階</x:v>
+      </x:c>
+      <x:c r="E188" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタの Stage=Migration</x:v>
+      </x:c>
+      <x:c r="F188" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G188" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H188" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I188" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J188" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K188" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L188" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="63" customHeight="1">
+      <x:c r="A189" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B189" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C189" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D189" s="166" t="str">
+        <x:v>サポート終了日 / 移行期限日</x:v>
+      </x:c>
+      <x:c r="E189" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタの Date</x:v>
+      </x:c>
+      <x:c r="F189" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G189" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H189" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I189" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J189" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K189" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L189" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="63" customHeight="1">
+      <x:c r="A190" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B190" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C190" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D190" s="166" t="str">
+        <x:v>期限までの残日数</x:v>
+      </x:c>
+      <x:c r="E190" s="166" t="str">
+        <x:v>期限日 - 判定日</x:v>
+      </x:c>
+      <x:c r="F190" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G190" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H190" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I190" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J190" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K190" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L190" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="63" customHeight="1">
+      <x:c r="A191" s="165" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B191" s="166" t="str">
+        <x:v>製品ライフサイクル</x:v>
+      </x:c>
+      <x:c r="C191" s="166" t="str">
+        <x:v>製品移行期間中</x:v>
+      </x:c>
+      <x:c r="D191" s="166" t="str">
+        <x:v>ライフサイクル指摘判定</x:v>
+      </x:c>
+      <x:c r="E191" s="166" t="str">
+        <x:v>ソフトウェア名 / バージョンとライフサイクルマスタの照合結果</x:v>
+      </x:c>
+      <x:c r="F191" s="166" t="str">
+        <x:v>顧客製品ライフサイクルマスタ / 算出項目</x:v>
+      </x:c>
+      <x:c r="G191" s="166" t="str">
+        <x:v>標準 SG-SCCM CMDB ターゲット項目なし</x:v>
+      </x:c>
+      <x:c r="H191" s="166" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I191" s="171" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J191" s="166" t="str">
+        <x:v>ソフトウェアインストール情報は標準格納できる。サポート終了および移行判定は MECM の原始インベントリ項目ではない。</x:v>
+      </x:c>
+      <x:c r="K191" s="166" t="str">
+        <x:v>顧客ルール</x:v>
+      </x:c>
+      <x:c r="L191" s="166" t="str">
+        <x:v>https://www.servicenow.com/docs/r/zurich/servicenow-platform/service-graph-connectors/cmdb-sccm-classes.html
+https://learn.microsoft.com/en-us/intune/configmgr/develop/core/understand/sqlviews/hardware-inventory-views-configuration-manager</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A3:L5"/>
+    <x:mergeCell ref="B8:F8"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
